--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95397FD4-559D-4659-8178-DA065DC24AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972E2D00-AF37-42DE-A375-853A8E93BDF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Record" sheetId="1" r:id="rId1"/>
@@ -23,9 +23,9 @@
     <sheet name="Economy" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reciept!$B$4:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reciept!$B$4:$E$22</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="144">
   <si>
     <t>Weekly Sales:</t>
   </si>
@@ -472,6 +472,12 @@
   </si>
   <si>
     <t xml:space="preserve"> &lt;type name="Cauldron"&gt;</t>
+  </si>
+  <si>
+    <t>Reindeer Pelt - Pristine</t>
+  </si>
+  <si>
+    <t>Reindeer Pelt - Worn</t>
   </si>
 </sst>
 </file>
@@ -614,19 +620,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -665,7 +662,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -696,9 +692,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -722,7 +715,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -873,13 +878,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304560</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>132825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -983,7 +988,7 @@
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>304560</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>79560</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1073,14 +1078,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>8280</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>112680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>307440</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>232200</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>232199</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1292,22 +1297,70 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>20672</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3073" name="AutoShape 1" descr="Winchester70">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6B8F100-73CF-6B47-8C26-7CEF988D88B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7764780" y="2926080"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>371007</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:colOff>723901</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>116363</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
+        <xdr:cNvPr id="4" name="Picture 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61C1CABF-7528-AE0F-B26B-707ACFDC5249}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BFBA6A0-09FA-4CC4-72B8-509F0F693BC5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1323,8 +1376,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7783547" y="581025"/>
-          <a:ext cx="4486090" cy="1644015"/>
+          <a:off x="7762876" y="542925"/>
+          <a:ext cx="4857750" cy="1383188"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1567,10 +1620,10 @@
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>45977</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>45985</v>
       </c>
     </row>
@@ -1630,77 +1683,77 @@
       </c>
     </row>
     <row r="17" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1712,7 +1765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="27.6640625" customWidth="1"/>
@@ -1788,659 +1841,663 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>45988</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>45988</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>45988</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>45990</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>45990</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="2">
         <v>45993</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="2">
         <v>45997</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>45998</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="2">
         <v>46003</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>46003</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <v>46003</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>46003</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="2">
         <v>46005</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="2">
         <v>46009</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="2">
         <v>46009</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="2">
         <v>46012</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="2">
         <v>46012</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="2">
         <v>45659</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="2">
         <v>45659</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>3</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
         <v>3</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>3</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7">
-        <v>1</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4">
         <v>3</v>
       </c>
-      <c r="M3" s="7">
-        <v>1</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
         <v>2</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="4">
         <v>5</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7">
-        <v>1</v>
-      </c>
-      <c r="S3" s="47">
-        <v>1</v>
-      </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="18"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+      <c r="S3" s="42">
+        <v>1</v>
+      </c>
+      <c r="T3" s="42">
+        <v>3</v>
+      </c>
+      <c r="U3" s="15"/>
     </row>
     <row r="4" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="18"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="42"/>
+      <c r="S4" s="42"/>
+      <c r="T4" s="42"/>
+      <c r="U4" s="15"/>
     </row>
     <row r="5" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4">
         <v>3</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="4">
         <v>2</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="4">
         <v>7</v>
       </c>
-      <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="7">
+      <c r="P5" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
         <v>5</v>
       </c>
-      <c r="R5" s="47">
-        <v>1</v>
-      </c>
-      <c r="S5" s="47">
-        <v>1</v>
-      </c>
-      <c r="T5" s="47">
+      <c r="R5" s="42">
+        <v>1</v>
+      </c>
+      <c r="S5" s="42">
+        <v>1</v>
+      </c>
+      <c r="T5" s="42">
+        <v>8</v>
+      </c>
+      <c r="U5" s="15"/>
+    </row>
+    <row r="6" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4">
+        <v>2</v>
+      </c>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="42">
+        <v>1</v>
+      </c>
+      <c r="U6" s="15"/>
+    </row>
+    <row r="7" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4">
+        <v>4</v>
+      </c>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="15"/>
+    </row>
+    <row r="8" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4">
+        <v>3</v>
+      </c>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="15"/>
+    </row>
+    <row r="9" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="3">
+        <v>2</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
+        <v>6</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
+        <v>4</v>
+      </c>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="42"/>
+      <c r="S9" s="42">
+        <v>1</v>
+      </c>
+      <c r="T9" s="42"/>
+      <c r="U9" s="15"/>
+    </row>
+    <row r="10" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U5" s="18"/>
-    </row>
-    <row r="6" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7">
-        <v>1</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7">
+      <c r="B10" s="3">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4">
+        <v>17</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4">
+        <v>9</v>
+      </c>
+      <c r="H10" s="4">
+        <v>28</v>
+      </c>
+      <c r="I10" s="4">
+        <v>9</v>
+      </c>
+      <c r="J10" s="4">
+        <v>16</v>
+      </c>
+      <c r="K10" s="4">
+        <v>9</v>
+      </c>
+      <c r="L10" s="4">
+        <v>12</v>
+      </c>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
+        <v>24</v>
+      </c>
+      <c r="O10" s="4">
+        <v>12</v>
+      </c>
+      <c r="P10" s="4">
+        <v>28</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>22</v>
+      </c>
+      <c r="R10" s="42">
+        <v>26</v>
+      </c>
+      <c r="S10" s="42">
+        <v>29</v>
+      </c>
+      <c r="T10" s="42">
+        <v>20</v>
+      </c>
+      <c r="U10" s="15"/>
+    </row>
+    <row r="11" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="18"/>
-    </row>
-    <row r="7" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6">
-        <v>2</v>
-      </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7">
-        <v>4</v>
-      </c>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47">
-        <v>2</v>
-      </c>
-      <c r="U7" s="18"/>
-    </row>
-    <row r="8" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7">
-        <v>3</v>
-      </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="18"/>
-    </row>
-    <row r="9" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4">
+        <v>1</v>
+      </c>
+      <c r="R11" s="42"/>
+      <c r="S11" s="42"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="15"/>
+    </row>
+    <row r="12" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3">
         <v>12</v>
       </c>
-      <c r="B9" s="6">
-        <v>2</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7">
-        <v>6</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7">
-        <v>1</v>
-      </c>
-      <c r="L9" s="7">
-        <v>4</v>
-      </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47">
-        <v>1</v>
-      </c>
-      <c r="T9" s="47">
-        <v>3</v>
-      </c>
-      <c r="U9" s="18"/>
-    </row>
-    <row r="10" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B10" s="6">
-        <v>6</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7">
-        <v>17</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
-        <v>9</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
+        <v>100</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
+        <v>111</v>
+      </c>
+      <c r="J12" s="4">
+        <v>142</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4">
+        <v>249</v>
+      </c>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4">
+        <v>58</v>
+      </c>
+      <c r="R12" s="42">
         <v>28</v>
       </c>
-      <c r="I10" s="7">
-        <v>9</v>
-      </c>
-      <c r="J10" s="7">
-        <v>16</v>
-      </c>
-      <c r="K10" s="7">
-        <v>9</v>
-      </c>
-      <c r="L10" s="7">
-        <v>12</v>
-      </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7">
-        <v>24</v>
-      </c>
-      <c r="O10" s="7">
-        <v>12</v>
-      </c>
-      <c r="P10" s="7">
-        <v>28</v>
-      </c>
-      <c r="Q10" s="7">
-        <v>22</v>
-      </c>
-      <c r="R10" s="47">
-        <v>26</v>
-      </c>
-      <c r="S10" s="47">
-        <v>29</v>
-      </c>
-      <c r="T10" s="47">
-        <v>21</v>
-      </c>
-      <c r="U10" s="18"/>
-    </row>
-    <row r="11" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" s="7">
-        <v>2</v>
-      </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7">
-        <v>1</v>
-      </c>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47">
-        <v>1</v>
-      </c>
-      <c r="U11" s="18"/>
-    </row>
-    <row r="12" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6">
-        <v>12</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6">
-        <v>49</v>
-      </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7">
-        <v>100</v>
-      </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7">
-        <v>111</v>
-      </c>
-      <c r="J12" s="7">
-        <v>142</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7">
-        <v>249</v>
-      </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7">
-        <v>58</v>
-      </c>
-      <c r="R12" s="47">
-        <v>28</v>
-      </c>
-      <c r="S12" s="47">
+      <c r="S12" s="42">
         <f>29+42+46+37</f>
         <v>154</v>
       </c>
-      <c r="T12" s="47">
-        <v>45</v>
-      </c>
-      <c r="U12" s="18"/>
+      <c r="T12" s="42">
+        <v>154</v>
+      </c>
+      <c r="U12" s="15"/>
     </row>
     <row r="13" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7">
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
         <v>2</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7">
-        <v>1</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4">
         <v>2</v>
       </c>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="47">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="42">
         <v>2</v>
       </c>
-      <c r="S13" s="47">
+      <c r="S13" s="42">
         <v>2</v>
       </c>
-      <c r="T13" s="47">
-        <v>1</v>
-      </c>
-      <c r="U13" s="18"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="15"/>
     </row>
     <row r="14" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4">
+        <v>1</v>
+      </c>
+      <c r="N14" s="4">
         <v>4</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="4">
         <v>5</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4">
         <v>2</v>
       </c>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47">
+      <c r="R14" s="42"/>
+      <c r="S14" s="42">
         <v>2</v>
       </c>
-      <c r="T14" s="47">
+      <c r="T14" s="42">
+        <v>3</v>
+      </c>
+      <c r="U14" s="15"/>
+    </row>
+    <row r="15" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
+        <v>2</v>
+      </c>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="42">
+        <v>3</v>
+      </c>
+      <c r="S15" s="42">
+        <v>5</v>
+      </c>
+      <c r="T15" s="42"/>
+      <c r="U15" s="15"/>
+    </row>
+    <row r="16" spans="1:21" ht="21" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4">
         <v>4</v>
       </c>
-      <c r="U14" s="18"/>
-    </row>
-    <row r="15" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7">
-        <v>1</v>
-      </c>
-      <c r="L15" s="7">
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
+        <v>3</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="42"/>
+      <c r="S16" s="42">
+        <v>1</v>
+      </c>
+      <c r="T16" s="42">
+        <v>1</v>
+      </c>
+      <c r="U16" s="15"/>
+    </row>
+    <row r="17" spans="1:20" ht="21" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="3">
+        <v>4</v>
+      </c>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
         <v>2</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="47">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
+        <v>2</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4">
         <v>3</v>
       </c>
-      <c r="S15" s="47">
-        <v>5</v>
-      </c>
-      <c r="T15" s="47">
-        <v>1</v>
-      </c>
-      <c r="U15" s="18"/>
-    </row>
-    <row r="16" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7">
-        <v>4</v>
-      </c>
-      <c r="I16" s="7">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="R17" s="42"/>
+      <c r="S17" s="42">
         <v>3</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47">
-        <v>1</v>
-      </c>
-      <c r="T16" s="47">
-        <v>5</v>
-      </c>
-      <c r="U16" s="18"/>
-    </row>
-    <row r="17" spans="1:20" ht="21" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="B17" s="6">
-        <v>4</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7">
+      <c r="T17" s="42">
         <v>2</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7">
-        <v>2</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7">
-        <v>1</v>
-      </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7">
-        <v>3</v>
-      </c>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47">
-        <v>3</v>
-      </c>
-      <c r="T17" s="47">
-        <v>2</v>
+    </row>
+    <row r="18" spans="1:20" ht="21" x14ac:dyDescent="0.4">
+      <c r="A18" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" ht="21" x14ac:dyDescent="0.4">
+      <c r="A19" s="15" t="s">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -2455,256 +2512,256 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
-    <col min="3" max="3" width="4.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="4.5546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" style="6" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="44"/>
+      <c r="E3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="10">
         <v>14</v>
       </c>
-      <c r="E4" s="14">
-        <f>VLOOKUP(B4,Economy!B3:I19,8,FALSE())*D4</f>
+      <c r="E4" s="11">
+        <f>VLOOKUP(B4,Economy!B3:I21,8,FALSE())*D4</f>
         <v>92400</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14">
-        <f>VLOOKUP(B5,Economy!B4:I20,8,FALSE())*D5</f>
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
+        <f>VLOOKUP(B5,Economy!B4:I22,8,FALSE())*D5</f>
         <v>5500</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="10">
         <v>8</v>
       </c>
-      <c r="E6" s="14">
-        <f>VLOOKUP(B6,Economy!B5:I21,8,FALSE())*D6</f>
+      <c r="E6" s="11">
+        <f>VLOOKUP(B6,Economy!B5:I23,8,FALSE())*D6</f>
         <v>134400</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="14">
-        <f>VLOOKUP(B7,Economy!B6:I22,8,FALSE())*D7</f>
+      <c r="E7" s="11">
+        <f>VLOOKUP(B7,Economy!B6:I24,8,FALSE())*D7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="10">
         <v>2</v>
       </c>
-      <c r="E8" s="14">
-        <f>VLOOKUP(B8,Economy!B7:I23,8,FALSE())*D8</f>
+      <c r="E8" s="11">
+        <f>VLOOKUP(B8,Economy!B7:I25,8,FALSE())*D8</f>
         <v>60000</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>0</v>
       </c>
-      <c r="E9" s="14">
-        <f>VLOOKUP(B9,Economy!B8:I24,8,FALSE())*D9</f>
+      <c r="E9" s="11">
+        <f>VLOOKUP(B9,Economy!B8:I26,8,FALSE())*D9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="10">
         <v>9</v>
       </c>
-      <c r="E10" s="14">
-        <f>VLOOKUP(B10,Economy!B9:I25,8,FALSE())*D10</f>
+      <c r="E10" s="11">
+        <f>VLOOKUP(B10,Economy!B9:I27,8,FALSE())*D10</f>
         <v>108000</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="10">
         <v>23</v>
       </c>
-      <c r="E11" s="14">
-        <f>VLOOKUP(B11,Economy!B10:I26,8,FALSE())*D11</f>
+      <c r="E11" s="11">
+        <f>VLOOKUP(B11,Economy!B10:I28,8,FALSE())*D11</f>
         <v>23000</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="14">
-        <f>VLOOKUP(B12,Economy!B11:I27,8,FALSE())*D12</f>
+      <c r="E12" s="11">
+        <f>VLOOKUP(B12,Economy!B11:I29,8,FALSE())*D12</f>
         <v>18000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="10">
         <v>161</v>
       </c>
-      <c r="E13" s="14">
-        <f>VLOOKUP(B13,Economy!B12:I28,8,FALSE())*D13</f>
+      <c r="E13" s="11">
+        <f>VLOOKUP(B13,Economy!B12:I30,8,FALSE())*D13</f>
         <v>120750</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <v>4</v>
       </c>
-      <c r="E14" s="14">
-        <f>VLOOKUP(B14,Economy!B13:I29,8,FALSE())*D14</f>
+      <c r="E14" s="11">
+        <f>VLOOKUP(B14,Economy!B13:I31,8,FALSE())*D14</f>
         <v>12000</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="10">
         <v>0</v>
       </c>
-      <c r="E15" s="14">
-        <f>VLOOKUP(B15,Economy!B14:I30,8,FALSE())*D15</f>
+      <c r="E15" s="11">
+        <f>VLOOKUP(B15,Economy!B14:I32,8,FALSE())*D15</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <f>VLOOKUP(B16,Economy!B15:I31,8,FALSE())*D16</f>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11">
+        <f>VLOOKUP(B16,Economy!B15:I33,8,FALSE())*D16</f>
         <v>9000</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <f>VLOOKUP(B17,Economy!B16:I32,8,FALSE())*D17</f>
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
+        <f>VLOOKUP(B17,Economy!B16:I34,8,FALSE())*D17</f>
         <v>7000</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="10">
         <v>4</v>
       </c>
-      <c r="E18" s="14">
-        <f>VLOOKUP(B18,Economy!B17:I33,8,FALSE())*D18</f>
+      <c r="E18" s="11">
+        <f>VLOOKUP(B18,Economy!B17:I35,8,FALSE())*D18</f>
         <v>24000</v>
       </c>
     </row>
@@ -2723,7 +2780,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -2735,183 +2792,187 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L1" s="15"/>
+      <c r="L1" s="12"/>
     </row>
     <row r="2" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="L2" s="15"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="L2" s="12"/>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="L3" s="15"/>
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="L3" s="12"/>
     </row>
     <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="15"/>
+      <c r="L4" s="12"/>
     </row>
     <row r="5" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="19">
-        <f>VLOOKUP(B5,Economy!B3:I19,8,FALSE())*D5</f>
+      <c r="D5" s="4"/>
+      <c r="E5" s="16">
+        <f>VLOOKUP(B5,Economy!B:I,8,FALSE())*D5</f>
         <v>0</v>
       </c>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="18" t="s">
+      <c r="L5" s="12"/>
+    </row>
+    <row r="6" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="19">
-        <f>VLOOKUP(B6,Economy!B4:I20,8,FALSE())*D6</f>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="16">
+        <f>VLOOKUP(B6,Economy!B:I,8,FALSE())*D6</f>
+        <v>5500</v>
+      </c>
+      <c r="L6" s="12"/>
+    </row>
+    <row r="7" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4</v>
+      </c>
+      <c r="E7" s="16">
+        <f>VLOOKUP(B7,Economy!B:I,8,FALSE())*D7</f>
+        <v>67200</v>
+      </c>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="16">
+        <f>VLOOKUP(B8,Economy!B:I,8,FALSE())*D8</f>
+        <v>14000</v>
+      </c>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="9" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="16">
+        <f>VLOOKUP(B9,Economy!B:I,8,FALSE())*D9</f>
         <v>0</v>
       </c>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="L9" s="12"/>
+    </row>
+    <row r="10" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="7">
-        <v>8</v>
-      </c>
-      <c r="E7" s="19">
-        <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
-        <v>134400</v>
-      </c>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="16">
+        <f>VLOOKUP(B10,Economy!B:I,8,FALSE())*D10</f>
+        <v>25000</v>
+      </c>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="19">
-        <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
+      <c r="D11" s="4">
+        <v>2</v>
+      </c>
+      <c r="E11" s="16">
+        <f>VLOOKUP(B11,Economy!B:I,8,FALSE())*D11</f>
+        <v>24000</v>
+      </c>
+      <c r="L11" s="12"/>
+    </row>
+    <row r="12" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="16">
+        <f>VLOOKUP(B12,Economy!B:I,8,FALSE())*D12</f>
         <v>0</v>
       </c>
-      <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="L12" s="12"/>
+    </row>
+    <row r="13" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="7">
-        <v>2</v>
-      </c>
-      <c r="E9" s="19">
-        <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
-        <v>60000</v>
-      </c>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="16">
+        <f>VLOOKUP(B13,Economy!B:I,8,FALSE())*D13</f>
+        <v>0</v>
+      </c>
+      <c r="L13" s="12"/>
+    </row>
+    <row r="14" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="19">
-        <f>VLOOKUP(B10,Economy!B8:I24,8,FALSE())*D10</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="19">
-        <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D12" s="7">
-        <v>12</v>
-      </c>
-      <c r="E12" s="19">
-        <f>VLOOKUP(B12,Economy!B10:I26,8,FALSE())*D12</f>
-        <v>12000</v>
-      </c>
-      <c r="L12" s="15"/>
-    </row>
-    <row r="13" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="19">
-        <f>VLOOKUP(B13,Economy!B11:I27,8,FALSE())*D13</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="19">
-        <f>VLOOKUP(B14,Economy!B12:I28,8,FALSE())*D14</f>
+      <c r="D14" s="4"/>
+      <c r="E14" s="16">
+        <f>VLOOKUP(B14,Economy!B:I,8,FALSE())*D14</f>
         <v>0</v>
       </c>
       <c r="H14">
@@ -2931,70 +2992,68 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="19">
-        <f>VLOOKUP(B15,Economy!B13:I29,8,FALSE())*D15</f>
+      <c r="D15" s="4"/>
+      <c r="E15" s="16">
+        <f>VLOOKUP(B15,Economy!B:I,8,FALSE())*D15</f>
         <v>0</v>
       </c>
-      <c r="L15" s="15"/>
-    </row>
-    <row r="16" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="18" t="s">
+      <c r="L15" s="12"/>
+    </row>
+    <row r="16" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="7">
-        <v>3</v>
-      </c>
-      <c r="E16" s="19">
-        <f>VLOOKUP(B16,Economy!B14:I30,8,FALSE())*D16</f>
-        <v>72000</v>
+      <c r="D16" s="4"/>
+      <c r="E16" s="16">
+        <f>VLOOKUP(B16,Economy!B:I,8,FALSE())*D16</f>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="19">
-        <f>VLOOKUP(B17,Economy!B15:I31,8,FALSE())*D17</f>
+      <c r="D17" s="4"/>
+      <c r="E17" s="16">
+        <f>VLOOKUP(B17,Economy!B:I,8,FALSE())*D17</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="19">
-        <f>VLOOKUP(B18,Economy!B16:I32,8,FALSE())*D18</f>
+      <c r="D18" s="4"/>
+      <c r="E18" s="16">
+        <f>VLOOKUP(B18,Economy!B:I,8,FALSE())*D18</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="19">
-        <f>VLOOKUP(B19,Economy!B17:I33,8,FALSE())*D19</f>
+      <c r="D19" s="4"/>
+      <c r="E19" s="16">
+        <f>VLOOKUP(B19,Economy!B:I,8,FALSE())*D19</f>
         <v>0</v>
       </c>
       <c r="J19" t="s">
@@ -3005,37 +3064,67 @@
       </c>
     </row>
     <row r="20" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="20"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18" t="s">
+      <c r="B20" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="16">
+        <f>VLOOKUP(B20,Economy!B:I,8,FALSE())*D20</f>
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="16">
+        <f>VLOOKUP(B21,Economy!B:I,8,FALSE())*D21</f>
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="21">
-        <f>SUM(E5:E19)</f>
-        <v>278400</v>
-      </c>
-      <c r="J20" s="22">
-        <f>$E$20/3</f>
-        <v>92800</v>
-      </c>
-      <c r="K20" s="22">
-        <f>$E$20/2</f>
-        <v>139200</v>
-      </c>
-      <c r="L20" s="22">
-        <f>$E$20/3</f>
-        <v>92800</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="23">
+      <c r="E22" s="17">
+        <f>SUM(E5:E20)</f>
+        <v>255700</v>
+      </c>
+      <c r="J22" s="18">
+        <f>$E$22/3</f>
+        <v>85233.333333333328</v>
+      </c>
+      <c r="K22" s="18">
+        <f>$E$22/2</f>
+        <v>127850</v>
+      </c>
+      <c r="L22" s="18">
+        <f>$E$22/3</f>
+        <v>85233.333333333328</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="19">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
+        <v>46034</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:E20" xr:uid="{00000000-0009-0000-0000-000003000000}">
+  <autoFilter ref="B4:E22" xr:uid="{00000000-0009-0000-0000-000003000000}">
     <filterColumn colId="2">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -3067,254 +3156,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
+      <c r="A1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="24"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="21"/>
+      <c r="G4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="21"/>
+      <c r="L4" s="21"/>
+      <c r="M4" s="21"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="20"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="24"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="21"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="20"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="24"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="21"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="20"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="24"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="20"/>
+      <c r="I7" s="20"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="21"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="20"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="24"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="21"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="20"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="21"/>
+      <c r="L8" s="21"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="20"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="24"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="21"/>
+      <c r="L9" s="21"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="20"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="24"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="21"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="20"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="24"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="21"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="20"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="24"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="21"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="20"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="24"/>
+      <c r="A13" s="20"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="20"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="20"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="24"/>
+      <c r="A14" s="20"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="20"/>
     </row>
     <row r="15" spans="1:15" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
-        <v>200000</v>
-      </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28">
+      <c r="A15" s="22"/>
+      <c r="B15" s="23">
+        <v>300000</v>
+      </c>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="24">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
-      </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27">
-        <v>150000</v>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="28">
+        <v>46034</v>
+      </c>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="23">
+        <v>350000</v>
+      </c>
+      <c r="K15" s="22"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="24">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
-      </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
+        <v>46034</v>
+      </c>
+      <c r="N15" s="22"/>
+      <c r="O15" s="22"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3337,311 +3426,311 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
     </row>
     <row r="3" spans="1:14" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="L3" s="5">
+      <c r="I3" s="27"/>
+      <c r="L3" s="2">
         <v>45986</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="2">
         <v>45992</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="2">
         <v>45999</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="29">
         <v>6600</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="M4" s="34">
+      <c r="I4" s="9"/>
+      <c r="M4" s="30">
         <v>3600</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="30">
         <v>3600</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="29">
         <v>5500</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="M5" s="33">
+      <c r="I5" s="9"/>
+      <c r="M5" s="29">
         <v>3000</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="29">
         <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="29">
         <v>16800</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="M6" s="34">
+      <c r="I6" s="9"/>
+      <c r="M6" s="30">
         <v>10800</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="30">
         <v>10800</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="29">
         <v>14000</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="M7" s="33">
+      <c r="I7" s="9"/>
+      <c r="M7" s="29">
         <v>9000</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="29">
         <v>9000</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="29">
         <v>30000</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="M8" s="34">
+      <c r="I8" s="9"/>
+      <c r="M8" s="30">
         <v>18600</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="30">
         <v>18600</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="29">
         <v>25000</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="M9" s="33">
+      <c r="I9" s="9"/>
+      <c r="M9" s="29">
         <v>15500</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="29">
         <v>15500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33">
+      <c r="C10" s="28"/>
+      <c r="D10" s="29">
         <v>12000</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="M10" s="33">
+      <c r="I10" s="9"/>
+      <c r="M10" s="29">
         <v>8000</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="29">
         <v>8000</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="29">
         <v>1000</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="M11" s="33">
+      <c r="I11" s="9"/>
+      <c r="M11" s="29">
         <v>1000</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="29">
         <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="29">
         <v>9000</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="M12" s="33">
+      <c r="I12" s="9"/>
+      <c r="M12" s="29">
         <v>7000</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="29">
         <v>7000</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="29">
         <v>750</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="M13" s="33">
+      <c r="I13" s="9"/>
+      <c r="M13" s="29">
         <v>500</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="29">
         <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <v>3000</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="M14" s="33">
+      <c r="I14" s="9"/>
+      <c r="M14" s="29">
         <v>2500</v>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="29">
         <v>2500</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="29">
         <v>24000</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="M15" s="33">
+      <c r="I15" s="9"/>
+      <c r="M15" s="29">
         <v>35000</v>
       </c>
-      <c r="N15" s="33">
+      <c r="N15" s="29">
         <v>35000</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="29">
         <v>9000</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="M16" s="33">
+      <c r="I16" s="9"/>
+      <c r="M16" s="29">
         <v>13500</v>
       </c>
-      <c r="N16" s="33">
+      <c r="N16" s="29">
         <v>13500</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="29">
         <v>7000</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="M17" s="33">
+      <c r="I17" s="9"/>
+      <c r="M17" s="29">
         <v>11000</v>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="29">
         <v>11000</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="29">
         <v>6000</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="29">
         <v>6000</v>
       </c>
-      <c r="N18" s="33">
+      <c r="N18" s="29">
         <v>6000</v>
       </c>
     </row>
@@ -3665,7 +3754,7 @@
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="22.21875" customWidth="1"/>
-    <col min="7" max="7" width="4.5546875" style="37" customWidth="1"/>
+    <col min="7" max="7" width="4.5546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="5.44140625" customWidth="1"/>
     <col min="10" max="10" width="27.21875" customWidth="1"/>
@@ -3674,293 +3763,293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="43" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
     </row>
     <row r="3" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="38" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="34"/>
+      <c r="F3" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="38" t="s">
+      <c r="G3" s="26"/>
+      <c r="H3" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="40"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="36">
         <v>300000</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="36"/>
+      <c r="F4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="36">
         <v>600000</v>
       </c>
-      <c r="I4" s="33"/>
+      <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="36">
         <v>100000</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="36">
         <v>500000</v>
       </c>
-      <c r="I5" s="33"/>
+      <c r="I5" s="29"/>
     </row>
     <row r="6" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="36">
         <v>500000</v>
       </c>
-      <c r="I6" s="33"/>
+      <c r="I6" s="29"/>
     </row>
     <row r="7" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="25"/>
+      <c r="D7" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="36">
         <v>500000</v>
       </c>
-      <c r="I7" s="33"/>
+      <c r="I7" s="29"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="36">
         <v>500000</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="36">
         <v>500000</v>
       </c>
-      <c r="I8" s="33"/>
+      <c r="I8" s="29"/>
     </row>
     <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="36">
         <v>500000</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="36">
         <v>400000</v>
       </c>
-      <c r="I9" s="33"/>
+      <c r="I9" s="29"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="36">
         <v>450000</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="36">
         <v>300000</v>
       </c>
-      <c r="I10" s="33"/>
+      <c r="I10" s="29"/>
     </row>
     <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="36">
         <v>400000</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="36">
         <v>200000</v>
       </c>
-      <c r="I11" s="33"/>
+      <c r="I11" s="29"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="36">
         <v>500000</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="36">
         <v>150000</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="42"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="37"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="36">
         <v>350000</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="36">
         <v>150000</v>
       </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="42"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="37"/>
     </row>
     <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="36">
         <v>250000</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="36">
         <v>150000</v>
       </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="42"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="37"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="36">
         <v>250000</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="30"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="F16" s="12"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3974,7 +4063,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:AA52"/>
+  <dimension ref="B1:AA54"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.44140625" customWidth="1"/>
@@ -3998,21 +4087,21 @@
       </c>
     </row>
     <row r="2" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -4077,13 +4166,13 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="44">
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="39">
         <f>MROUND(I5*1.2,100)</f>
         <v>6600</v>
       </c>
@@ -4112,7 +4201,7 @@
       <c r="H5">
         <v>1.7</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="40">
         <f>MROUND(G5*H5,500)</f>
         <v>5500</v>
       </c>
@@ -4121,17 +4210,17 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="44">
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="39">
         <f>MROUND(I7*1.2,100)</f>
         <v>16800</v>
       </c>
-      <c r="J6" s="44"/>
+      <c r="J6" s="39"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
@@ -4157,7 +4246,7 @@
       <c r="H7">
         <v>0.8</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="40">
         <f>MROUND(G7*H7,500)</f>
         <v>14000</v>
       </c>
@@ -4166,17 +4255,17 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="44">
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="39">
         <f>MROUND(I9*1.2,100)</f>
         <v>30000</v>
       </c>
-      <c r="J8" s="44"/>
+      <c r="J8" s="39"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -4202,7 +4291,7 @@
       <c r="H9">
         <v>0.8</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="40">
         <f>MROUND(G9*H9,500)</f>
         <v>25000</v>
       </c>
@@ -4231,11 +4320,11 @@
       <c r="H10">
         <v>1.55</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="40">
         <f>MROUND(G10*H10,500)</f>
         <v>12000</v>
       </c>
-      <c r="J10" s="46"/>
+      <c r="J10" s="41"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
@@ -4261,11 +4350,11 @@
       <c r="H11">
         <v>1.5</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="40">
         <f>MROUND(G11*H11,500)</f>
         <v>1000</v>
       </c>
-      <c r="J11" s="46"/>
+      <c r="J11" s="41"/>
       <c r="L11" t="s">
         <v>99</v>
       </c>
@@ -4312,11 +4401,11 @@
       <c r="H12">
         <v>2</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="40">
         <f>MROUND(G12*H12,500)</f>
         <v>9000</v>
       </c>
-      <c r="J12" s="46"/>
+      <c r="J12" s="41"/>
       <c r="M12" t="s">
         <v>99</v>
       </c>
@@ -4360,11 +4449,11 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="40">
         <f>MROUND(G13*H13,250)</f>
         <v>750</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="39"/>
       <c r="N13" t="s">
         <v>99</v>
       </c>
@@ -4399,11 +4488,11 @@
       <c r="H14">
         <v>4</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="40">
         <f>MROUND(G14*H14,500)</f>
         <v>3000</v>
       </c>
-      <c r="J14" s="46"/>
+      <c r="J14" s="41"/>
       <c r="M14" t="s">
         <v>99</v>
       </c>
@@ -4438,11 +4527,11 @@
       <c r="H15">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="40">
         <f>MROUND(G15*H15,500)</f>
         <v>24000</v>
       </c>
-      <c r="J15" s="46"/>
+      <c r="J15" s="41"/>
       <c r="S15" t="s">
         <v>99</v>
       </c>
@@ -4471,11 +4560,11 @@
       <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="40">
         <f>MROUND(G16*H16,500)</f>
         <v>9000</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="41"/>
       <c r="M16" t="s">
         <v>99</v>
       </c>
@@ -4513,11 +4602,11 @@
       <c r="H17">
         <v>2</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="40">
         <f>MROUND(G17*H17,500)</f>
         <v>7000</v>
       </c>
-      <c r="J17" s="46"/>
+      <c r="J17" s="41"/>
       <c r="L17" t="s">
         <v>99</v>
       </c>
@@ -4549,11 +4638,11 @@
       <c r="H18">
         <v>2</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="40">
         <f>MROUND(G18*H18,500)</f>
         <v>6000</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="41"/>
       <c r="L18" t="s">
         <v>99</v>
       </c>
@@ -4561,237 +4650,255 @@
         <v>99</v>
       </c>
     </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>142</v>
+      </c>
+      <c r="I19" s="40">
+        <v>40000</v>
+      </c>
+      <c r="J19" s="41"/>
+    </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
-        <v>101</v>
-      </c>
-      <c r="M20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="X21" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>105</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="I20" s="40">
+        <v>30000</v>
+      </c>
+      <c r="J20" s="41"/>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
+        <v>5</v>
+      </c>
+      <c r="C22" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" t="s">
+        <v>100</v>
+      </c>
+      <c r="K22" t="s">
+        <v>16</v>
+      </c>
+      <c r="L22" t="s">
+        <v>101</v>
+      </c>
+      <c r="M22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="X23" t="s">
         <v>102</v>
       </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="X22" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
+      <c r="Y23" t="s">
         <v>103</v>
       </c>
-      <c r="Y23" t="s">
-        <v>110</v>
-      </c>
       <c r="Z23" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="AA23" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" t="s">
+        <v>102</v>
+      </c>
+      <c r="X24" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y24" t="s">
         <v>107</v>
       </c>
-      <c r="Y24" s="9" t="s">
-        <v>113</v>
+      <c r="Z24" t="s">
+        <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y25" s="9" t="s">
-        <v>116</v>
+        <v>103</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>111</v>
       </c>
       <c r="AA25" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="Y26" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="AA26" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>120</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>118</v>
+        <v>115</v>
+      </c>
+      <c r="Y27" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
         <v>121</v>
       </c>
-      <c r="Y28" t="s">
+      <c r="Y30" t="s">
         <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Y29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Y30" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
       <c r="Y31" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="Y32" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y33" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B32" t="s">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>104</v>
       </c>
-      <c r="Y32" t="s">
+      <c r="Y34" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B33" t="s">
+    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
         <v>108</v>
       </c>
-      <c r="Y33" t="s">
+      <c r="Y35" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="Y34" t="s">
+    <row r="36" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y36" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="Y35" t="s">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y37" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B37" s="9" t="s">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B39" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B38" s="9" t="s">
+    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B40" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B39" s="9" t="s">
+    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B41" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B40" s="9" t="s">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B42" s="6" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
-        <v>134</v>
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B45" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
         <v>141</v>
       </c>
     </row>

--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95397FD4-559D-4659-8178-DA065DC24AF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF99A9F1-ABEB-421C-A41A-6749C210E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Record" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reciept!$B$4:$E$20</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -45,8 +45,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="143">
   <si>
     <t>Weekly Sales:</t>
   </si>
@@ -472,6 +494,9 @@
   </si>
   <si>
     <t xml:space="preserve"> &lt;type name="Cauldron"&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -619,15 +644,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -696,9 +712,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -722,7 +735,19 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -975,58 +1000,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>304560</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>79560</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="AutoShape 2" descr="Livonia - DayZ Wiki">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5821560" y="1047600"/>
-          <a:ext cx="304560" cy="298800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="0">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>111960</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -1101,6 +1074,89 @@
         <a:xfrm>
           <a:off x="1917000" y="3713040"/>
           <a:ext cx="652320" cy="519840"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>111960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>16560</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="527820" cy="462330"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55BE67D5-CD5F-443F-9FE6-39799A750E0A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="111960" y="344220"/>
+          <a:ext cx="527820" cy="462330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>588720</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>50940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7" descr="Sold PNG Images Transparent Free Download">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7DFC8956-7404-402D-B68C-7FAE080C9B1B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9928860" y="381000"/>
+          <a:ext cx="703020" cy="515760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1567,10 +1623,10 @@
       <c r="B2">
         <v>4</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>45977</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>45985</v>
       </c>
     </row>
@@ -1630,77 +1686,77 @@
       </c>
     </row>
     <row r="17" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -1788,658 +1844,658 @@
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="B2" s="5">
+      <c r="B2" s="2">
         <v>45988</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="2">
         <v>45988</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="2">
         <v>45988</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="2">
         <v>45990</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>45990</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="2">
         <v>45993</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="2">
         <v>45997</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="2">
         <v>45998</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="2">
         <v>46003</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="2">
         <v>46003</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="2">
         <v>46003</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="2">
         <v>46003</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="2">
         <v>46005</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="2">
         <v>46009</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="2">
         <v>46009</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="2">
         <v>46012</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="2">
         <v>46012</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="2">
         <v>45659</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="2">
         <v>45659</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>3</v>
       </c>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="C3" s="3"/>
+      <c r="D3" s="3">
         <v>3</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="4">
         <v>5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>3</v>
       </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7">
-        <v>1</v>
-      </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7">
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4">
         <v>3</v>
       </c>
-      <c r="M3" s="7">
-        <v>1</v>
-      </c>
-      <c r="N3" s="7">
+      <c r="M3" s="4">
+        <v>1</v>
+      </c>
+      <c r="N3" s="4">
         <v>2</v>
       </c>
-      <c r="O3" s="7">
+      <c r="O3" s="4">
         <v>5</v>
       </c>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7">
-        <v>1</v>
-      </c>
-      <c r="S3" s="47">
-        <v>1</v>
-      </c>
-      <c r="T3" s="47"/>
-      <c r="U3" s="18"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="4"/>
+      <c r="R3" s="4">
+        <v>1</v>
+      </c>
+      <c r="S3" s="43">
+        <v>1</v>
+      </c>
+      <c r="T3" s="43"/>
+      <c r="U3" s="15"/>
     </row>
     <row r="4" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="7">
-        <v>1</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
-      <c r="O4" s="7"/>
-      <c r="P4" s="7"/>
-      <c r="Q4" s="7"/>
-      <c r="R4" s="47"/>
-      <c r="S4" s="47"/>
-      <c r="T4" s="47"/>
-      <c r="U4" s="18"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="15"/>
     </row>
     <row r="5" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>4</v>
       </c>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6">
+      <c r="C5" s="3"/>
+      <c r="D5" s="3">
         <v>4</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7">
-        <v>1</v>
-      </c>
-      <c r="L5" s="7"/>
-      <c r="M5" s="7">
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="4"/>
+      <c r="M5" s="4">
         <v>3</v>
       </c>
-      <c r="N5" s="7">
+      <c r="N5" s="4">
         <v>2</v>
       </c>
-      <c r="O5" s="7">
+      <c r="O5" s="4">
         <v>7</v>
       </c>
-      <c r="P5" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="7">
+      <c r="P5" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="4">
         <v>5</v>
       </c>
-      <c r="R5" s="47">
-        <v>1</v>
-      </c>
-      <c r="S5" s="47">
-        <v>1</v>
-      </c>
-      <c r="T5" s="47">
+      <c r="R5" s="43">
+        <v>1</v>
+      </c>
+      <c r="S5" s="43">
+        <v>1</v>
+      </c>
+      <c r="T5" s="43">
         <v>5</v>
       </c>
-      <c r="U5" s="18"/>
+      <c r="U5" s="15"/>
     </row>
     <row r="6" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7">
-        <v>1</v>
-      </c>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7">
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4">
+        <v>1</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4">
         <v>2</v>
       </c>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7">
-        <v>1</v>
-      </c>
-      <c r="P6" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="7"/>
-      <c r="R6" s="47"/>
-      <c r="S6" s="47"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="18"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4">
+        <v>1</v>
+      </c>
+      <c r="P6" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="15"/>
     </row>
     <row r="7" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
         <v>2</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7">
+      <c r="D7" s="3"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4">
         <v>4</v>
       </c>
-      <c r="R7" s="47"/>
-      <c r="S7" s="47"/>
-      <c r="T7" s="47">
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="43">
         <v>2</v>
       </c>
-      <c r="U7" s="18"/>
+      <c r="U7" s="15"/>
     </row>
     <row r="8" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4">
         <v>3</v>
       </c>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="7"/>
-      <c r="R8" s="47"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="18"/>
+      <c r="O8" s="4"/>
+      <c r="P8" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="43"/>
+      <c r="U8" s="15"/>
     </row>
     <row r="9" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7">
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4">
         <v>6</v>
       </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7">
-        <v>1</v>
-      </c>
-      <c r="L9" s="7">
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4">
+        <v>1</v>
+      </c>
+      <c r="L9" s="4">
         <v>4</v>
       </c>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7">
-        <v>1</v>
-      </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="47"/>
-      <c r="S9" s="47">
-        <v>1</v>
-      </c>
-      <c r="T9" s="47">
+      <c r="M9" s="4"/>
+      <c r="N9" s="4"/>
+      <c r="O9" s="4">
+        <v>1</v>
+      </c>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43">
+        <v>1</v>
+      </c>
+      <c r="T9" s="43">
         <v>3</v>
       </c>
-      <c r="U9" s="18"/>
+      <c r="U9" s="15"/>
     </row>
     <row r="10" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>6</v>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7">
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="4">
         <v>17</v>
       </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4">
         <v>9</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="4">
         <v>28</v>
       </c>
-      <c r="I10" s="7">
+      <c r="I10" s="4">
         <v>9</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="4">
         <v>16</v>
       </c>
-      <c r="K10" s="7">
+      <c r="K10" s="4">
         <v>9</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="4">
         <v>12</v>
       </c>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7">
+      <c r="M10" s="4"/>
+      <c r="N10" s="4">
         <v>24</v>
       </c>
-      <c r="O10" s="7">
+      <c r="O10" s="4">
         <v>12</v>
       </c>
-      <c r="P10" s="7">
+      <c r="P10" s="4">
         <v>28</v>
       </c>
-      <c r="Q10" s="7">
+      <c r="Q10" s="4">
         <v>22</v>
       </c>
-      <c r="R10" s="47">
+      <c r="R10" s="43">
         <v>26</v>
       </c>
-      <c r="S10" s="47">
+      <c r="S10" s="43">
         <v>29</v>
       </c>
-      <c r="T10" s="47">
+      <c r="T10" s="43">
         <v>21</v>
       </c>
-      <c r="U10" s="18"/>
+      <c r="U10" s="15"/>
     </row>
     <row r="11" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6"/>
-      <c r="E11" s="7">
-        <v>1</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7">
-        <v>1</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7">
-        <v>1</v>
-      </c>
-      <c r="L11" s="7">
+      <c r="B11" s="3"/>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4">
+        <v>1</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4">
+        <v>1</v>
+      </c>
+      <c r="L11" s="4">
         <v>2</v>
       </c>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7">
-        <v>1</v>
-      </c>
-      <c r="R11" s="47"/>
-      <c r="S11" s="47"/>
-      <c r="T11" s="47">
-        <v>1</v>
-      </c>
-      <c r="U11" s="18"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4">
+        <v>1</v>
+      </c>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="43">
+        <v>1</v>
+      </c>
+      <c r="U11" s="15"/>
     </row>
     <row r="12" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>12</v>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6">
+      <c r="C12" s="3"/>
+      <c r="D12" s="3">
         <v>49</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7">
+      <c r="E12" s="4"/>
+      <c r="F12" s="4">
         <v>100</v>
       </c>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
         <v>111</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="4">
         <v>142</v>
       </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7">
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4">
         <v>249</v>
       </c>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="7">
+      <c r="O12" s="4"/>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="4">
         <v>58</v>
       </c>
-      <c r="R12" s="47">
+      <c r="R12" s="43">
         <v>28</v>
       </c>
-      <c r="S12" s="47">
+      <c r="S12" s="43">
         <f>29+42+46+37</f>
         <v>154</v>
       </c>
-      <c r="T12" s="47">
+      <c r="T12" s="43">
         <v>45</v>
       </c>
-      <c r="U12" s="18"/>
+      <c r="U12" s="15"/>
     </row>
     <row r="13" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6">
-        <v>1</v>
-      </c>
-      <c r="C13" s="6">
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
         <v>3</v>
       </c>
-      <c r="D13" s="6"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7">
-        <v>1</v>
-      </c>
-      <c r="H13" s="7">
+      <c r="D13" s="3"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4">
+        <v>1</v>
+      </c>
+      <c r="H13" s="4">
         <v>2</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7">
-        <v>1</v>
-      </c>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7">
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4">
+        <v>1</v>
+      </c>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4">
         <v>2</v>
       </c>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="47">
+      <c r="Q13" s="4"/>
+      <c r="R13" s="43">
         <v>2</v>
       </c>
-      <c r="S13" s="47">
+      <c r="S13" s="43">
         <v>2</v>
       </c>
-      <c r="T13" s="47">
-        <v>1</v>
-      </c>
-      <c r="U13" s="18"/>
+      <c r="T13" s="43">
+        <v>1</v>
+      </c>
+      <c r="U13" s="15"/>
     </row>
     <row r="14" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7">
-        <v>1</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7">
-        <v>1</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4">
+        <v>1</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4">
+        <v>1</v>
+      </c>
+      <c r="N14" s="4">
         <v>4</v>
       </c>
-      <c r="O14" s="7">
+      <c r="O14" s="4">
         <v>5</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="7">
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4">
         <v>2</v>
       </c>
-      <c r="R14" s="47"/>
-      <c r="S14" s="47">
+      <c r="R14" s="43"/>
+      <c r="S14" s="43">
         <v>2</v>
       </c>
-      <c r="T14" s="47">
+      <c r="T14" s="43">
         <v>4</v>
       </c>
-      <c r="U14" s="18"/>
+      <c r="U14" s="15"/>
     </row>
     <row r="15" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="7">
-        <v>1</v>
-      </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7">
-        <v>1</v>
-      </c>
-      <c r="L15" s="7">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4">
+        <v>1</v>
+      </c>
+      <c r="L15" s="4">
         <v>2</v>
       </c>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="47">
+      <c r="M15" s="4"/>
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="43">
         <v>3</v>
       </c>
-      <c r="S15" s="47">
+      <c r="S15" s="43">
         <v>5</v>
       </c>
-      <c r="T15" s="47">
-        <v>1</v>
-      </c>
-      <c r="U15" s="18"/>
+      <c r="T15" s="43">
+        <v>1</v>
+      </c>
+      <c r="U15" s="15"/>
     </row>
     <row r="16" spans="1:21" ht="21" x14ac:dyDescent="0.4">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4">
         <v>4</v>
       </c>
-      <c r="I16" s="7">
-        <v>1</v>
-      </c>
-      <c r="J16" s="7">
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+      <c r="J16" s="4">
         <v>3</v>
       </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="47"/>
-      <c r="S16" s="47">
-        <v>1</v>
-      </c>
-      <c r="T16" s="47">
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43">
+        <v>1</v>
+      </c>
+      <c r="T16" s="43">
         <v>5</v>
       </c>
-      <c r="U16" s="18"/>
+      <c r="U16" s="15"/>
     </row>
     <row r="17" spans="1:20" ht="21" x14ac:dyDescent="0.4">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="3">
         <v>4</v>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4">
         <v>2</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7">
+      <c r="I17" s="4"/>
+      <c r="J17" s="4">
         <v>2</v>
       </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7">
-        <v>1</v>
-      </c>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="7">
+      <c r="K17" s="4"/>
+      <c r="L17" s="4">
+        <v>1</v>
+      </c>
+      <c r="M17" s="4"/>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4">
         <v>3</v>
       </c>
-      <c r="R17" s="47"/>
-      <c r="S17" s="47">
+      <c r="R17" s="43"/>
+      <c r="S17" s="43">
         <v>3</v>
       </c>
-      <c r="T17" s="47">
+      <c r="T17" s="43">
         <v>2</v>
       </c>
     </row>
@@ -2455,255 +2511,255 @@
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
-    <col min="3" max="3" width="4.5546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.5546875" style="9" customWidth="1"/>
+    <col min="3" max="3" width="4.5546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.5546875" style="6" customWidth="1"/>
     <col min="5" max="5" width="16.109375" customWidth="1"/>
     <col min="6" max="6" width="13.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
     <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="45"/>
+      <c r="E3" s="8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D4" s="10">
         <v>14</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="11">
         <f>VLOOKUP(B4,Economy!B3:I19,8,FALSE())*D4</f>
         <v>92400</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="13">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="D5" s="10">
+        <v>1</v>
+      </c>
+      <c r="E5" s="11">
         <f>VLOOKUP(B5,Economy!B4:I20,8,FALSE())*D5</f>
         <v>5500</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D6" s="10">
         <v>8</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="11">
         <f>VLOOKUP(B6,Economy!B5:I21,8,FALSE())*D6</f>
         <v>134400</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="10">
         <v>0</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="11">
         <f>VLOOKUP(B7,Economy!B6:I22,8,FALSE())*D7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="10">
         <v>2</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="11">
         <f>VLOOKUP(B8,Economy!B7:I23,8,FALSE())*D8</f>
         <v>60000</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="10">
         <v>0</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <f>VLOOKUP(B9,Economy!B8:I24,8,FALSE())*D9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D10" s="10">
         <v>9</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <f>VLOOKUP(B10,Economy!B9:I25,8,FALSE())*D10</f>
         <v>108000</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D11" s="10">
         <v>23</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="11">
         <f>VLOOKUP(B11,Economy!B10:I26,8,FALSE())*D11</f>
         <v>23000</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="10">
         <v>2</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="11">
         <f>VLOOKUP(B12,Economy!B11:I27,8,FALSE())*D12</f>
         <v>18000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D13" s="10">
         <v>161</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="11">
         <f>VLOOKUP(B13,Economy!B12:I28,8,FALSE())*D13</f>
         <v>120750</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="10">
         <v>4</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="11">
         <f>VLOOKUP(B14,Economy!B13:I29,8,FALSE())*D14</f>
         <v>12000</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="10">
         <v>0</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="11">
         <f>VLOOKUP(B15,Economy!B14:I30,8,FALSE())*D15</f>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="13">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="11">
         <f>VLOOKUP(B16,Economy!B15:I31,8,FALSE())*D16</f>
         <v>9000</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="13">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
+      <c r="D17" s="10">
+        <v>1</v>
+      </c>
+      <c r="E17" s="11">
         <f>VLOOKUP(B17,Economy!B16:I32,8,FALSE())*D17</f>
         <v>7000</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="10">
         <v>4</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="11">
         <f>VLOOKUP(B18,Economy!B17:I33,8,FALSE())*D18</f>
         <v>24000</v>
       </c>
@@ -2722,328 +2778,421 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
     <col min="3" max="4" width="5.88671875" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="4.88671875" customWidth="1"/>
+    <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L1" s="15"/>
-    </row>
-    <row r="2" spans="1:12" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+    <row r="1" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L1" s="12"/>
+    </row>
+    <row r="2" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="L2" s="15"/>
-    </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="17" t="s">
+      <c r="B2" s="46"/>
+      <c r="C2" s="46"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="H2" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+    </row>
+    <row r="3" spans="1:13" ht="22.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="L3" s="20">
+        <f ca="1">TODAY()</f>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="14"/>
+      <c r="D4" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="15"/>
-    </row>
-    <row r="5" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="18" t="s">
+    </row>
+    <row r="5" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="19">
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="16">
         <f>VLOOKUP(B5,Economy!B3:I19,8,FALSE())*D5</f>
+        <v>6600</v>
+      </c>
+      <c r="I5" s="15" t="str" cm="1">
+        <f t="array" ref="I5:L9">_xlfn._xlws.FILTER(B5:E20,E5:E20&gt;0,"")</f>
+        <v>Pristine Hare Pelt</v>
+      </c>
+      <c r="J5" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K5" s="4">
+        <v>1</v>
+      </c>
+      <c r="L5" s="16">
+        <v>6600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="4">
+        <v>2</v>
+      </c>
+      <c r="E6" s="16">
+        <f>VLOOKUP(B6,Economy!B4:I20,8,FALSE())*D6</f>
+        <v>11000</v>
+      </c>
+      <c r="I6" s="15" t="str">
+        <v>Hare Pelt</v>
+      </c>
+      <c r="J6" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K6" s="4">
+        <v>2</v>
+      </c>
+      <c r="L6" s="16">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B7" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="16">
+        <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
+        <v>50400</v>
+      </c>
+      <c r="I7" s="15" t="str">
+        <v>Pristine Deer Pelt</v>
+      </c>
+      <c r="J7" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K7" s="4">
+        <v>3</v>
+      </c>
+      <c r="L7" s="16">
+        <v>50400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B8" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="4">
+        <v>4</v>
+      </c>
+      <c r="E8" s="16">
+        <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
+        <v>56000</v>
+      </c>
+      <c r="I8" s="15" t="str">
+        <v>Deer Pelt</v>
+      </c>
+      <c r="J8" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K8" s="4">
+        <v>4</v>
+      </c>
+      <c r="L8" s="16">
+        <v>56000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="16">
+        <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
         <v>0</v>
       </c>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="I9" s="15" t="str">
+        <v xml:space="preserve">  </v>
+      </c>
+      <c r="J9" s="4" t="str">
+        <v xml:space="preserve">  </v>
+      </c>
+      <c r="K9" s="4" t="str">
+        <v>TOTAL:</v>
+      </c>
+      <c r="L9" s="16">
+        <v>124000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B10" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="19">
-        <f>VLOOKUP(B6,Economy!B4:I20,8,FALSE())*D6</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="15"/>
-    </row>
-    <row r="7" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B7" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="7">
-        <v>8</v>
-      </c>
-      <c r="E7" s="19">
-        <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
-        <v>134400</v>
-      </c>
-      <c r="L7" s="15"/>
-    </row>
-    <row r="8" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B8" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="19">
-        <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="15"/>
-    </row>
-    <row r="9" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B9" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="7">
-        <v>2</v>
-      </c>
-      <c r="E9" s="19">
-        <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
-        <v>60000</v>
-      </c>
-      <c r="L9" s="15"/>
-    </row>
-    <row r="10" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B10" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="19">
+      <c r="D10" s="4"/>
+      <c r="E10" s="16">
         <f>VLOOKUP(B10,Economy!B8:I24,8,FALSE())*D10</f>
         <v>0</v>
       </c>
-      <c r="L10" s="15"/>
-    </row>
-    <row r="11" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="18" t="s">
+      <c r="I10" s="15"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="16"/>
+    </row>
+    <row r="11" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="19">
+      <c r="D11" s="4"/>
+      <c r="E11" s="16">
         <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
         <v>0</v>
       </c>
-      <c r="L11" s="15"/>
-    </row>
-    <row r="12" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B12" s="18" t="s">
+      <c r="I11" s="15"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="16"/>
+    </row>
+    <row r="12" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="7">
-        <v>12</v>
-      </c>
-      <c r="E12" s="19">
+      <c r="D12" s="4"/>
+      <c r="E12" s="16">
         <f>VLOOKUP(B12,Economy!B10:I26,8,FALSE())*D12</f>
-        <v>12000</v>
-      </c>
-      <c r="L12" s="15"/>
-    </row>
-    <row r="13" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B13" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="16"/>
+    </row>
+    <row r="13" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B13" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="19">
+      <c r="D13" s="4"/>
+      <c r="E13" s="16">
         <f>VLOOKUP(B13,Economy!B11:I27,8,FALSE())*D13</f>
         <v>0</v>
       </c>
-      <c r="L13" s="15"/>
-    </row>
-    <row r="14" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B14" s="18" t="s">
+      <c r="I13" s="15"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="16"/>
+    </row>
+    <row r="14" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B14" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="19">
+      <c r="D14" s="4"/>
+      <c r="E14" s="16">
         <f>VLOOKUP(B14,Economy!B12:I28,8,FALSE())*D14</f>
         <v>0</v>
       </c>
-      <c r="H14">
-        <v>36</v>
-      </c>
-      <c r="I14">
-        <v>14</v>
-      </c>
-      <c r="J14">
-        <v>100</v>
-      </c>
-      <c r="K14">
-        <v>71</v>
-      </c>
-      <c r="L14">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B15" s="18" t="s">
+      <c r="I14" s="15"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="16"/>
+    </row>
+    <row r="15" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="19">
+      <c r="D15" s="4"/>
+      <c r="E15" s="16">
         <f>VLOOKUP(B15,Economy!B13:I29,8,FALSE())*D15</f>
         <v>0</v>
       </c>
-      <c r="L15" s="15"/>
-    </row>
-    <row r="16" spans="1:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="18" t="s">
+      <c r="I15" s="15"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="16"/>
+    </row>
+    <row r="16" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="7">
-        <v>3</v>
-      </c>
-      <c r="E16" s="19">
+      <c r="D16" s="4"/>
+      <c r="E16" s="16">
         <f>VLOOKUP(B16,Economy!B14:I30,8,FALSE())*D16</f>
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B17" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="I16" s="15"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="16"/>
+    </row>
+    <row r="17" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="19">
+      <c r="D17" s="4"/>
+      <c r="E17" s="16">
         <f>VLOOKUP(B17,Economy!B15:I31,8,FALSE())*D17</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B18" s="18" t="s">
+      <c r="I17" s="15"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="16"/>
+    </row>
+    <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B18" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="19">
+      <c r="D18" s="4"/>
+      <c r="E18" s="16">
         <f>VLOOKUP(B18,Economy!B16:I32,8,FALSE())*D18</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="2:12" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B19" s="18" t="s">
+      <c r="I18" s="15"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="16"/>
+    </row>
+    <row r="19" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B19" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="19">
+      <c r="D19" s="4"/>
+      <c r="E19" s="16">
         <f>VLOOKUP(B19,Economy!B17:I33,8,FALSE())*D19</f>
         <v>0</v>
       </c>
-      <c r="J19" t="s">
-        <v>39</v>
-      </c>
-      <c r="K19" t="s">
-        <v>40</v>
-      </c>
+      <c r="I19" s="15"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="16"/>
     </row>
     <row r="20" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="20"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18" t="s">
+      <c r="B20" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="21">
+      <c r="E20" s="18">
         <f>SUM(E5:E19)</f>
-        <v>278400</v>
-      </c>
-      <c r="J20" s="22">
-        <f>$E$20/3</f>
-        <v>92800</v>
-      </c>
-      <c r="K20" s="22">
-        <f>$E$20/2</f>
-        <v>139200</v>
-      </c>
-      <c r="L20" s="22">
-        <f>$E$20/3</f>
-        <v>92800</v>
-      </c>
+        <v>124000</v>
+      </c>
+      <c r="I20" s="17"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="18"/>
     </row>
     <row r="21" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="23">
+      <c r="B22" s="20">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J25" t="s">
+        <v>39</v>
+      </c>
+      <c r="K25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J26" s="19">
+        <f>$E$20/3</f>
+        <v>41333.333333333336</v>
+      </c>
+      <c r="K26" s="19">
+        <f>$E$20/2</f>
+        <v>62000</v>
+      </c>
+      <c r="L26" s="19">
+        <f>$E$20/3</f>
+        <v>41333.333333333336</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:E20" xr:uid="{00000000-0009-0000-0000-000003000000}">
-    <filterColumn colId="2">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
-  <mergeCells count="1">
+  <autoFilter ref="B4:E20" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="H2:M2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3067,254 +3216,254 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="24"/>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
+      <c r="A1" s="21"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="24"/>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
-      <c r="L2" s="24"/>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="24"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="I3" s="24"/>
-      <c r="J3" s="24"/>
-      <c r="K3" s="24"/>
-      <c r="L3" s="24"/>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
+      <c r="I3" s="21"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+      <c r="L3" s="21"/>
+      <c r="M3" s="21"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="21"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="24"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="24"/>
-      <c r="I4" s="24"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="25"/>
-      <c r="L4" s="25"/>
-      <c r="M4" s="25"/>
-      <c r="N4" s="25"/>
-      <c r="O4" s="24"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="21"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="24"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="24"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="21"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="24"/>
-      <c r="I6" s="24"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="L6" s="25"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
-      <c r="O6" s="24"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
+      <c r="O6" s="21"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="24"/>
-      <c r="I7" s="24"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="L7" s="25"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
-      <c r="O7" s="24"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="21"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="22"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="22"/>
+      <c r="O7" s="21"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A8" s="24"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="24"/>
-      <c r="I8" s="24"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="24"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="21"/>
+      <c r="I8" s="21"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="22"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="22"/>
+      <c r="O8" s="21"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A9" s="24"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
-      <c r="O9" s="24"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="22"/>
+      <c r="O9" s="21"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A10" s="24"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="24"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="25"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
-      <c r="O10" s="24"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="22"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="22"/>
+      <c r="O10" s="21"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A11" s="24"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="25"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
-      <c r="O11" s="24"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="21"/>
+      <c r="I11" s="21"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="22"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="22"/>
+      <c r="O11" s="21"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A12" s="24"/>
-      <c r="B12" s="25"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="24"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="25"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
-      <c r="O12" s="24"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="21"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="22"/>
+      <c r="O12" s="21"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="25"/>
-      <c r="G13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="25"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
-      <c r="O13" s="24"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="21"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="22"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="22"/>
+      <c r="O13" s="21"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="25"/>
-      <c r="G14" s="24"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="25"/>
-      <c r="K14" s="25"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="25"/>
-      <c r="N14" s="25"/>
-      <c r="O14" s="24"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="22"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="22"/>
+      <c r="O14" s="21"/>
     </row>
     <row r="15" spans="1:15" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24">
         <v>200000</v>
       </c>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="28">
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
-      </c>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="27">
+        <v>46037</v>
+      </c>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24">
         <v>150000</v>
       </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="28">
+      <c r="K15" s="23"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46024</v>
-      </c>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
+        <v>46037</v>
+      </c>
+      <c r="N15" s="23"/>
+      <c r="O15" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3337,311 +3486,311 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="54.75" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="44" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
     </row>
     <row r="3" spans="1:14" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="31"/>
-      <c r="L3" s="5">
+      <c r="I3" s="28"/>
+      <c r="L3" s="2">
         <v>45986</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3" s="2">
         <v>45992</v>
       </c>
-      <c r="N3" s="5">
+      <c r="N3" s="2">
         <v>45999</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="30">
         <v>6600</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="M4" s="34">
+      <c r="I4" s="9"/>
+      <c r="M4" s="31">
         <v>3600</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="31">
         <v>3600</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="30">
         <v>5500</v>
       </c>
-      <c r="I5" s="12"/>
-      <c r="M5" s="33">
+      <c r="I5" s="9"/>
+      <c r="M5" s="30">
         <v>3000</v>
       </c>
-      <c r="N5" s="33">
+      <c r="N5" s="30">
         <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="32" t="s">
+      <c r="C6" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="30">
         <v>16800</v>
       </c>
-      <c r="I6" s="12"/>
-      <c r="M6" s="34">
+      <c r="I6" s="9"/>
+      <c r="M6" s="31">
         <v>10800</v>
       </c>
-      <c r="N6" s="34">
+      <c r="N6" s="31">
         <v>10800</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="32" t="s">
+      <c r="C7" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="30">
         <v>14000</v>
       </c>
-      <c r="I7" s="12"/>
-      <c r="M7" s="33">
+      <c r="I7" s="9"/>
+      <c r="M7" s="30">
         <v>9000</v>
       </c>
-      <c r="N7" s="33">
+      <c r="N7" s="30">
         <v>9000</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="30">
         <v>30000</v>
       </c>
-      <c r="I8" s="12"/>
-      <c r="M8" s="34">
+      <c r="I8" s="9"/>
+      <c r="M8" s="31">
         <v>18600</v>
       </c>
-      <c r="N8" s="34">
+      <c r="N8" s="31">
         <v>18600</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="30">
         <v>25000</v>
       </c>
-      <c r="I9" s="12"/>
-      <c r="M9" s="33">
+      <c r="I9" s="9"/>
+      <c r="M9" s="30">
         <v>15500</v>
       </c>
-      <c r="N9" s="33">
+      <c r="N9" s="30">
         <v>15500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33">
+      <c r="C10" s="29"/>
+      <c r="D10" s="30">
         <v>12000</v>
       </c>
-      <c r="I10" s="12"/>
-      <c r="M10" s="33">
+      <c r="I10" s="9"/>
+      <c r="M10" s="30">
         <v>8000</v>
       </c>
-      <c r="N10" s="33">
+      <c r="N10" s="30">
         <v>8000</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="33">
+      <c r="D11" s="30">
         <v>1000</v>
       </c>
-      <c r="I11" s="12"/>
-      <c r="M11" s="33">
+      <c r="I11" s="9"/>
+      <c r="M11" s="30">
         <v>1000</v>
       </c>
-      <c r="N11" s="33">
+      <c r="N11" s="30">
         <v>1000</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="30">
         <v>9000</v>
       </c>
-      <c r="I12" s="12"/>
-      <c r="M12" s="33">
+      <c r="I12" s="9"/>
+      <c r="M12" s="30">
         <v>7000</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="30">
         <v>7000</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="30">
         <v>750</v>
       </c>
-      <c r="I13" s="12"/>
-      <c r="M13" s="33">
+      <c r="I13" s="9"/>
+      <c r="M13" s="30">
         <v>500</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="30">
         <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="30">
         <v>3000</v>
       </c>
-      <c r="I14" s="12"/>
-      <c r="M14" s="33">
+      <c r="I14" s="9"/>
+      <c r="M14" s="30">
         <v>2500</v>
       </c>
-      <c r="N14" s="33">
+      <c r="N14" s="30">
         <v>2500</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="33">
+      <c r="D15" s="30">
         <v>24000</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="I15" s="12"/>
-      <c r="M15" s="33">
+      <c r="I15" s="9"/>
+      <c r="M15" s="30">
         <v>35000</v>
       </c>
-      <c r="N15" s="33">
+      <c r="N15" s="30">
         <v>35000</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="32" t="s">
+      <c r="C16" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="33">
+      <c r="D16" s="30">
         <v>9000</v>
       </c>
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="I16" s="12"/>
-      <c r="M16" s="33">
+      <c r="I16" s="9"/>
+      <c r="M16" s="30">
         <v>13500</v>
       </c>
-      <c r="N16" s="33">
+      <c r="N16" s="30">
         <v>13500</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="33">
+      <c r="D17" s="30">
         <v>7000</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="12"/>
-      <c r="M17" s="33">
+      <c r="I17" s="9"/>
+      <c r="M17" s="30">
         <v>11000</v>
       </c>
-      <c r="N17" s="33">
+      <c r="N17" s="30">
         <v>11000</v>
       </c>
     </row>
     <row r="18" spans="2:14" ht="21" x14ac:dyDescent="0.4">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="33">
+      <c r="D18" s="30">
         <v>6000</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="M18" s="33">
+      <c r="M18" s="30">
         <v>6000</v>
       </c>
-      <c r="N18" s="33">
+      <c r="N18" s="30">
         <v>6000</v>
       </c>
     </row>
@@ -3665,7 +3814,7 @@
     <col min="4" max="4" width="13.88671875" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
     <col min="6" max="6" width="22.21875" customWidth="1"/>
-    <col min="7" max="7" width="4.5546875" style="37" customWidth="1"/>
+    <col min="7" max="7" width="4.5546875" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.88671875" customWidth="1"/>
     <col min="9" max="9" width="5.44140625" customWidth="1"/>
     <col min="10" max="10" width="27.21875" customWidth="1"/>
@@ -3674,293 +3823,293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="54.75" customHeight="1" x14ac:dyDescent="1.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
     </row>
     <row r="3" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="38" t="s">
+      <c r="C3" s="27"/>
+      <c r="D3" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="29" t="s">
+      <c r="E3" s="35"/>
+      <c r="F3" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="30"/>
-      <c r="H3" s="38" t="s">
+      <c r="G3" s="27"/>
+      <c r="H3" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="I3" s="40"/>
+      <c r="I3" s="36"/>
     </row>
     <row r="4" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="37">
         <v>300000</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="37"/>
+      <c r="F4" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H4" s="41">
+      <c r="H4" s="37">
         <v>600000</v>
       </c>
-      <c r="I4" s="33"/>
+      <c r="I4" s="30"/>
     </row>
     <row r="5" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="32" t="s">
+      <c r="C5" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="37">
         <v>100000</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="37">
         <v>500000</v>
       </c>
-      <c r="I5" s="33"/>
+      <c r="I5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="37">
         <v>500000</v>
       </c>
-      <c r="I6" s="33"/>
+      <c r="I6" s="30"/>
     </row>
     <row r="7" spans="1:12" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="30" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="32" t="s">
+      <c r="G7" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="37">
         <v>500000</v>
       </c>
-      <c r="I7" s="33"/>
+      <c r="I7" s="30"/>
     </row>
     <row r="8" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="32" t="s">
+      <c r="C8" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="37">
         <v>500000</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="37">
         <v>500000</v>
       </c>
-      <c r="I8" s="33"/>
+      <c r="I8" s="30"/>
     </row>
     <row r="9" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="37">
         <v>500000</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="37">
         <v>400000</v>
       </c>
-      <c r="I9" s="33"/>
+      <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="32" t="s">
+      <c r="C10" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="37">
         <v>450000</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="37">
         <v>300000</v>
       </c>
-      <c r="I10" s="33"/>
+      <c r="I10" s="30"/>
     </row>
     <row r="11" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="37">
         <v>400000</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G11" s="32" t="s">
+      <c r="G11" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="37">
         <v>200000</v>
       </c>
-      <c r="I11" s="33"/>
+      <c r="I11" s="30"/>
     </row>
     <row r="12" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="32" t="s">
+      <c r="C12" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="37">
         <v>500000</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="37">
         <v>150000</v>
       </c>
-      <c r="I12" s="33"/>
-      <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="42"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="38"/>
     </row>
     <row r="13" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="32" t="s">
+      <c r="C13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="37">
         <v>350000</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="37">
         <v>150000</v>
       </c>
-      <c r="I13" s="33"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="42"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="9"/>
+      <c r="K13" s="9"/>
+      <c r="L13" s="38"/>
     </row>
     <row r="14" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="32" t="s">
+      <c r="C14" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="37">
         <v>250000</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="37">
         <v>150000</v>
       </c>
-      <c r="I14" s="33"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="42"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="9"/>
+      <c r="K14" s="9"/>
+      <c r="L14" s="38"/>
     </row>
     <row r="15" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="32" t="s">
+      <c r="C15" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="37">
         <v>250000</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="30"/>
+      <c r="J15" s="31"/>
+      <c r="K15" s="31"/>
     </row>
     <row r="16" spans="1:12" ht="21" x14ac:dyDescent="0.4">
-      <c r="F16" s="12"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3998,21 +4147,21 @@
       </c>
     </row>
     <row r="2" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="47"/>
+      <c r="M2" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.3">
       <c r="C3" t="s">
@@ -4077,13 +4226,13 @@
       <c r="B4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="43"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43"/>
-      <c r="H4" s="43"/>
-      <c r="I4" s="44">
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="40">
         <f>MROUND(I5*1.2,100)</f>
         <v>6600</v>
       </c>
@@ -4112,7 +4261,7 @@
       <c r="H5">
         <v>1.7</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="41">
         <f>MROUND(G5*H5,500)</f>
         <v>5500</v>
       </c>
@@ -4121,17 +4270,17 @@
       <c r="B6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="44">
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="40">
         <f>MROUND(I7*1.2,100)</f>
         <v>16800</v>
       </c>
-      <c r="J6" s="44"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
@@ -4157,7 +4306,7 @@
       <c r="H7">
         <v>0.8</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="41">
         <f>MROUND(G7*H7,500)</f>
         <v>14000</v>
       </c>
@@ -4166,17 +4315,17 @@
       <c r="B8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="44">
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="40">
         <f>MROUND(I9*1.2,100)</f>
         <v>30000</v>
       </c>
-      <c r="J8" s="44"/>
+      <c r="J8" s="40"/>
     </row>
     <row r="9" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
@@ -4202,7 +4351,7 @@
       <c r="H9">
         <v>0.8</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="41">
         <f>MROUND(G9*H9,500)</f>
         <v>25000</v>
       </c>
@@ -4231,11 +4380,11 @@
       <c r="H10">
         <v>1.55</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="41">
         <f>MROUND(G10*H10,500)</f>
         <v>12000</v>
       </c>
-      <c r="J10" s="46"/>
+      <c r="J10" s="42"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
@@ -4261,11 +4410,11 @@
       <c r="H11">
         <v>1.5</v>
       </c>
-      <c r="I11" s="45">
+      <c r="I11" s="41">
         <f>MROUND(G11*H11,500)</f>
         <v>1000</v>
       </c>
-      <c r="J11" s="46"/>
+      <c r="J11" s="42"/>
       <c r="L11" t="s">
         <v>99</v>
       </c>
@@ -4312,11 +4461,11 @@
       <c r="H12">
         <v>2</v>
       </c>
-      <c r="I12" s="45">
+      <c r="I12" s="41">
         <f>MROUND(G12*H12,500)</f>
         <v>9000</v>
       </c>
-      <c r="J12" s="46"/>
+      <c r="J12" s="42"/>
       <c r="M12" t="s">
         <v>99</v>
       </c>
@@ -4360,11 +4509,11 @@
       <c r="H13">
         <v>1</v>
       </c>
-      <c r="I13" s="45">
+      <c r="I13" s="41">
         <f>MROUND(G13*H13,250)</f>
         <v>750</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="40"/>
       <c r="N13" t="s">
         <v>99</v>
       </c>
@@ -4399,11 +4548,11 @@
       <c r="H14">
         <v>4</v>
       </c>
-      <c r="I14" s="45">
+      <c r="I14" s="41">
         <f>MROUND(G14*H14,500)</f>
         <v>3000</v>
       </c>
-      <c r="J14" s="46"/>
+      <c r="J14" s="42"/>
       <c r="M14" t="s">
         <v>99</v>
       </c>
@@ -4438,11 +4587,11 @@
       <c r="H15">
         <v>2.0499999999999998</v>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="41">
         <f>MROUND(G15*H15,500)</f>
         <v>24000</v>
       </c>
-      <c r="J15" s="46"/>
+      <c r="J15" s="42"/>
       <c r="S15" t="s">
         <v>99</v>
       </c>
@@ -4471,11 +4620,11 @@
       <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16" s="45">
+      <c r="I16" s="41">
         <f>MROUND(G16*H16,500)</f>
         <v>9000</v>
       </c>
-      <c r="J16" s="46"/>
+      <c r="J16" s="42"/>
       <c r="M16" t="s">
         <v>99</v>
       </c>
@@ -4513,11 +4662,11 @@
       <c r="H17">
         <v>2</v>
       </c>
-      <c r="I17" s="45">
+      <c r="I17" s="41">
         <f>MROUND(G17*H17,500)</f>
         <v>7000</v>
       </c>
-      <c r="J17" s="46"/>
+      <c r="J17" s="42"/>
       <c r="L17" t="s">
         <v>99</v>
       </c>
@@ -4549,11 +4698,11 @@
       <c r="H18">
         <v>2</v>
       </c>
-      <c r="I18" s="45">
+      <c r="I18" s="41">
         <f>MROUND(G18*H18,500)</f>
         <v>6000</v>
       </c>
-      <c r="J18" s="46"/>
+      <c r="J18" s="42"/>
       <c r="L18" t="s">
         <v>99</v>
       </c>
@@ -4639,7 +4788,7 @@
       <c r="B24" t="s">
         <v>107</v>
       </c>
-      <c r="Y24" s="9" t="s">
+      <c r="Y24" s="6" t="s">
         <v>113</v>
       </c>
       <c r="AA24" t="s">
@@ -4650,7 +4799,7 @@
       <c r="B25" t="s">
         <v>115</v>
       </c>
-      <c r="Y25" s="9" t="s">
+      <c r="Y25" s="6" t="s">
         <v>116</v>
       </c>
       <c r="AA25" t="s">
@@ -4726,22 +4875,22 @@
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B37" s="9" t="s">
+      <c r="B37" s="6" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B38" s="9" t="s">
+      <c r="B38" s="6" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="6" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B40" s="9" t="s">
+      <c r="B40" s="6" t="s">
         <v>131</v>
       </c>
     </row>

--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF99A9F1-ABEB-421C-A41A-6749C210E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C0AC89-1EE9-42E2-A0BA-E3C5CD1ED8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2871,24 +2871,22 @@
       <c r="C6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="4">
-        <v>2</v>
-      </c>
+      <c r="D6" s="4"/>
       <c r="E6" s="16">
         <f>VLOOKUP(B6,Economy!B4:I20,8,FALSE())*D6</f>
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="15" t="str">
-        <v>Hare Pelt</v>
+        <v>Pristine Deer Pelt</v>
       </c>
       <c r="J6" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K6" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L6" s="16">
-        <v>11000</v>
+        <v>50400</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2906,16 +2904,16 @@
         <v>50400</v>
       </c>
       <c r="I7" s="15" t="str">
-        <v>Pristine Deer Pelt</v>
+        <v>Deer Pelt</v>
       </c>
       <c r="J7" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K7" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L7" s="16">
-        <v>50400</v>
+        <v>56000</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2933,16 +2931,16 @@
         <v>56000</v>
       </c>
       <c r="I8" s="15" t="str">
-        <v>Deer Pelt</v>
+        <v>Leather Full Stack</v>
       </c>
       <c r="J8" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K8" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L8" s="16">
-        <v>56000</v>
+        <v>72000</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2967,7 +2965,7 @@
         <v>TOTAL:</v>
       </c>
       <c r="L9" s="16">
-        <v>124000</v>
+        <v>185000</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2994,10 +2992,12 @@
       <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>6</v>
+      </c>
       <c r="E11" s="16">
         <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="4"/>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="E20" s="18">
         <f>SUM(E5:E19)</f>
-        <v>124000</v>
+        <v>185000</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="15"/>
@@ -3177,15 +3177,15 @@
     <row r="26" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J26" s="19">
         <f>$E$20/3</f>
-        <v>41333.333333333336</v>
+        <v>61666.666666666664</v>
       </c>
       <c r="K26" s="19">
         <f>$E$20/2</f>
-        <v>62000</v>
+        <v>92500</v>
       </c>
       <c r="L26" s="19">
         <f>$E$20/3</f>
-        <v>41333.333333333336</v>
+        <v>61666.666666666664</v>
       </c>
     </row>
   </sheetData>

--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C0AC89-1EE9-42E2-A0BA-E3C5CD1ED8A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BD9A1F-F011-4C1B-8A1E-DD20211B21AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="1110" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Record" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
   <si>
     <t>Weekly Sales:</t>
   </si>
@@ -497,6 +497,12 @@
   </si>
   <si>
     <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>Spray Can</t>
+  </si>
+  <si>
+    <t>Rituals Books</t>
   </si>
 </sst>
 </file>
@@ -905,7 +911,7 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>304560</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>132825</xdr:rowOff>
+      <xdr:rowOff>136635</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1009,7 +1015,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>37800</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>478890</xdr:rowOff>
+      <xdr:rowOff>475080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1134,9 +1140,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>588720</xdr:colOff>
+      <xdr:colOff>592530</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>50940</xdr:rowOff>
+      <xdr:rowOff>54750</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1169,6 +1175,131 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="304560" cy="304560"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 1" descr="Livonia - DayZ Wiki">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B717DD1-E190-4762-ABC1-D5048B22A965}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5410200" y="0"/>
+          <a:ext cx="304560" cy="304560"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </xdr:style>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>111960</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>16560</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="527820" cy="462330"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9383C2F4-13F5-4874-B432-36C2FBAB87C0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5522160" y="344220"/>
+          <a:ext cx="527820" cy="462330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>1028700</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="703020" cy="515760"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9" descr="Sold PNG Images Transparent Free Download">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68D86DB4-0E18-4492-AF3D-BA7E1059CBC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9915525" y="381000"/>
+          <a:ext cx="703020" cy="515760"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1842,6 +1973,9 @@
       <c r="T1" t="s">
         <v>22</v>
       </c>
+      <c r="U1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" s="2">
@@ -1900,6 +2034,9 @@
       </c>
       <c r="T2" s="2">
         <v>45659</v>
+      </c>
+      <c r="U2" s="2">
+        <v>46048</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="21" x14ac:dyDescent="0.4">
@@ -2023,7 +2160,9 @@
       <c r="T5" s="43">
         <v>5</v>
       </c>
-      <c r="U5" s="15"/>
+      <c r="U5" s="15">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
@@ -2212,7 +2351,9 @@
       <c r="T10" s="43">
         <v>21</v>
       </c>
-      <c r="U10" s="15"/>
+      <c r="U10" s="15">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
@@ -2251,7 +2392,9 @@
       <c r="T11" s="43">
         <v>1</v>
       </c>
-      <c r="U11" s="15"/>
+      <c r="U11" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
@@ -2297,7 +2440,9 @@
       <c r="T12" s="43">
         <v>45</v>
       </c>
-      <c r="U12" s="15"/>
+      <c r="U12" s="15">
+        <v>33</v>
+      </c>
     </row>
     <row r="13" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A13" s="3" t="s">
@@ -2420,7 +2565,9 @@
       <c r="T15" s="43">
         <v>1</v>
       </c>
-      <c r="U15" s="15"/>
+      <c r="U15" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
@@ -2459,9 +2606,11 @@
       <c r="T16" s="43">
         <v>5</v>
       </c>
-      <c r="U16" s="15"/>
-    </row>
-    <row r="17" spans="1:20" ht="21" x14ac:dyDescent="0.4">
+      <c r="U16" s="15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="21" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
         <v>31</v>
       </c>
@@ -2497,6 +2646,9 @@
       </c>
       <c r="T17" s="43">
         <v>2</v>
+      </c>
+      <c r="U17">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2778,7 +2930,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:T26"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -2789,12 +2941,18 @@
     <col min="10" max="10" width="11.44140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.6640625" customWidth="1"/>
+    <col min="15" max="15" width="4.88671875" customWidth="1"/>
+    <col min="16" max="16" width="22" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L1" s="12"/>
-    </row>
-    <row r="2" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="S1" s="12"/>
+    </row>
+    <row r="2" spans="1:20" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="46" t="s">
         <v>37</v>
       </c>
@@ -2811,8 +2969,16 @@
       <c r="K2" s="46"/>
       <c r="L2" s="46"/>
       <c r="M2" s="46"/>
-    </row>
-    <row r="3" spans="1:13" ht="22.2" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="O2" s="46" t="s">
+        <v>37</v>
+      </c>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+    </row>
+    <row r="3" spans="1:20" ht="22.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -2821,10 +2987,14 @@
       <c r="F3" s="13"/>
       <c r="L3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46048</v>
+      </c>
+      <c r="S3" s="20">
+        <f ca="1">TODAY()</f>
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14" t="s">
         <v>33</v>
       </c>
@@ -2836,35 +3006,45 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
+      <c r="D5" s="4"/>
       <c r="E5" s="16">
         <f>VLOOKUP(B5,Economy!B3:I19,8,FALSE())*D5</f>
-        <v>6600</v>
+        <v>0</v>
       </c>
       <c r="I5" s="15" t="str" cm="1">
         <f t="array" ref="I5:L9">_xlfn._xlws.FILTER(B5:E20,E5:E20&gt;0,"")</f>
-        <v>Pristine Hare Pelt</v>
+        <v>Pristine Bear Pelt</v>
       </c>
       <c r="J5" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K5" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L5" s="16">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>60000</v>
+      </c>
+      <c r="P5" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R5" s="4">
+        <v>6</v>
+      </c>
+      <c r="S5" s="16">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B6" s="15" t="s">
         <v>11</v>
       </c>
@@ -2877,83 +3057,93 @@
         <v>0</v>
       </c>
       <c r="I6" s="15" t="str">
-        <v>Pristine Deer Pelt</v>
+        <v>Bear Pelt</v>
       </c>
       <c r="J6" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K6" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" s="16">
-        <v>50400</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>50000</v>
+      </c>
+      <c r="P6" s="15"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="16"/>
+    </row>
+    <row r="7" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4">
-        <v>3</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="16">
         <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
-        <v>50400</v>
+        <v>0</v>
       </c>
       <c r="I7" s="15" t="str">
-        <v>Deer Pelt</v>
+        <v>Cigarettes</v>
       </c>
       <c r="J7" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K7" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" s="16">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>2000</v>
+      </c>
+      <c r="P7" s="15"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="16"/>
+    </row>
+    <row r="8" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B8" s="15" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="4">
-        <v>4</v>
-      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="16">
         <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="I8" s="15" t="str">
-        <v>Leather Full Stack</v>
+        <v>Bible</v>
       </c>
       <c r="J8" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K8" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L8" s="16">
-        <v>72000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>60000</v>
+      </c>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="16"/>
+    </row>
+    <row r="9" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B9" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="4">
+        <v>2</v>
+      </c>
       <c r="E9" s="16">
         <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="I9" s="15" t="str">
         <v xml:space="preserve">  </v>
@@ -2965,63 +3155,81 @@
         <v>TOTAL:</v>
       </c>
       <c r="L9" s="16">
-        <v>185000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+        <v>172000</v>
+      </c>
+      <c r="P9" s="15"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="16"/>
+    </row>
+    <row r="10" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B10" s="15" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="4"/>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
       <c r="E10" s="16">
         <f>VLOOKUP(B10,Economy!B8:I24,8,FALSE())*D10</f>
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="I10" s="15"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="16"/>
-    </row>
-    <row r="11" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P10" s="15"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="16"/>
+    </row>
+    <row r="11" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B11" s="15" t="s">
         <v>12</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4">
-        <v>6</v>
-      </c>
+      <c r="D11" s="4"/>
       <c r="E11" s="16">
         <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="I11" s="15"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="16"/>
-    </row>
-    <row r="12" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P11" s="15"/>
+      <c r="Q11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="16"/>
+    </row>
+    <row r="12" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B12" s="15" t="s">
         <v>5</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="4"/>
+      <c r="D12" s="4">
+        <v>2</v>
+      </c>
       <c r="E12" s="16">
         <f>VLOOKUP(B12,Economy!B10:I26,8,FALSE())*D12</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="I12" s="15"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="16"/>
-    </row>
-    <row r="13" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P12" s="15"/>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="16"/>
+    </row>
+    <row r="13" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B13" s="15" t="s">
         <v>14</v>
       </c>
@@ -3037,8 +3245,12 @@
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="16"/>
-    </row>
-    <row r="14" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P13" s="15"/>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="16"/>
+    </row>
+    <row r="14" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B14" s="15" t="s">
         <v>28</v>
       </c>
@@ -3054,8 +3266,12 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="16"/>
-    </row>
-    <row r="15" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P14" s="15"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="16"/>
+    </row>
+    <row r="15" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B15" s="15" t="s">
         <v>29</v>
       </c>
@@ -3071,8 +3287,12 @@
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="16"/>
-    </row>
-    <row r="16" spans="1:13" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P15" s="15"/>
+      <c r="Q15" s="4"/>
+      <c r="R15" s="4"/>
+      <c r="S15" s="16"/>
+    </row>
+    <row r="16" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B16" s="15" t="s">
         <v>16</v>
       </c>
@@ -3088,10 +3308,14 @@
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="16"/>
-    </row>
-    <row r="17" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P16" s="15"/>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="16"/>
+    </row>
+    <row r="17" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B17" s="15" t="s">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>38</v>
@@ -3105,8 +3329,12 @@
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="16"/>
-    </row>
-    <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P17" s="15"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="16"/>
+    </row>
+    <row r="18" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B18" s="15" t="s">
         <v>30</v>
       </c>
@@ -3122,25 +3350,35 @@
       <c r="J18" s="4"/>
       <c r="K18" s="4"/>
       <c r="L18" s="16"/>
-    </row>
-    <row r="19" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P18" s="15"/>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="16"/>
+    </row>
+    <row r="19" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B19" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="4"/>
+      <c r="D19" s="4">
+        <v>10</v>
+      </c>
       <c r="E19" s="16">
         <f>VLOOKUP(B19,Economy!B17:I33,8,FALSE())*D19</f>
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="16"/>
-    </row>
-    <row r="20" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P19" s="15"/>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="16"/>
+    </row>
+    <row r="20" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B20" s="17" t="s">
         <v>142</v>
       </c>
@@ -3152,47 +3390,70 @@
       </c>
       <c r="E20" s="18">
         <f>SUM(E5:E19)</f>
-        <v>185000</v>
+        <v>172000</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="15"/>
       <c r="K20" s="15"/>
       <c r="L20" s="18"/>
-    </row>
-    <row r="21" spans="2:12" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="P20" s="17"/>
+      <c r="Q20" s="15"/>
+      <c r="R20" s="15"/>
+      <c r="S20" s="18"/>
+    </row>
+    <row r="21" spans="2:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="20">
         <f ca="1">TODAY()</f>
-        <v>46037</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="25" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J25" t="s">
         <v>39</v>
       </c>
       <c r="K25" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="26" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q25" t="s">
+        <v>39</v>
+      </c>
+      <c r="R25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J26" s="19">
         <f>$E$20/3</f>
-        <v>61666.666666666664</v>
+        <v>57333.333333333336</v>
       </c>
       <c r="K26" s="19">
         <f>$E$20/2</f>
-        <v>92500</v>
+        <v>86000</v>
       </c>
       <c r="L26" s="19">
         <f>$E$20/3</f>
-        <v>61666.666666666664</v>
+        <v>57333.333333333336</v>
+      </c>
+      <c r="Q26" s="19">
+        <f>$E$20/3</f>
+        <v>57333.333333333336</v>
+      </c>
+      <c r="R26" s="19">
+        <f>$E$20/2</f>
+        <v>86000</v>
+      </c>
+      <c r="S26" s="19">
+        <f>$E$20/3</f>
+        <v>57333.333333333336</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B4:E20" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="H2:M2"/>
+    <mergeCell ref="O2:T2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3448,7 +3709,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
@@ -3460,7 +3721,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46037</v>
+        <v>46048</v>
       </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>

--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2BD9A1F-F011-4C1B-8A1E-DD20211B21AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0BC241-F69F-4598-AC16-03EEA151E3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="1110" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Record" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2987,11 +2987,11 @@
       <c r="F3" s="13"/>
       <c r="L3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46048</v>
+        <v>46072</v>
       </c>
       <c r="S3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46048</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3013,23 +3013,25 @@
       <c r="C5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
       <c r="E5" s="16">
         <f>VLOOKUP(B5,Economy!B3:I19,8,FALSE())*D5</f>
-        <v>0</v>
+        <v>19800</v>
       </c>
       <c r="I5" s="15" t="str" cm="1">
-        <f t="array" ref="I5:L9">_xlfn._xlws.FILTER(B5:E20,E5:E20&gt;0,"")</f>
-        <v>Pristine Bear Pelt</v>
+        <f t="array" ref="I5:L15">_xlfn._xlws.FILTER(B5:E20,E5:E20&gt;0,"")</f>
+        <v>Pristine Hare Pelt</v>
       </c>
       <c r="J5" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K5" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L5" s="16">
-        <v>60000</v>
+        <v>19800</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>144</v>
@@ -3057,16 +3059,16 @@
         <v>0</v>
       </c>
       <c r="I6" s="15" t="str">
-        <v>Bear Pelt</v>
+        <v>Pristine Deer Pelt</v>
       </c>
       <c r="J6" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K6" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L6" s="16">
-        <v>50000</v>
+        <v>67200</v>
       </c>
       <c r="P6" s="15"/>
       <c r="Q6" s="4"/>
@@ -3080,13 +3082,15 @@
       <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="4">
+        <v>4</v>
+      </c>
       <c r="E7" s="16">
         <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
-        <v>0</v>
+        <v>67200</v>
       </c>
       <c r="I7" s="15" t="str">
-        <v>Cigarettes</v>
+        <v>Deer Pelt</v>
       </c>
       <c r="J7" s="4" t="str">
         <v xml:space="preserve"> - X</v>
@@ -3095,7 +3099,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="16">
-        <v>2000</v>
+        <v>28000</v>
       </c>
       <c r="P7" s="15"/>
       <c r="Q7" s="4"/>
@@ -3109,22 +3113,24 @@
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="4">
+        <v>2</v>
+      </c>
       <c r="E8" s="16">
         <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
-        <v>0</v>
+        <v>28000</v>
       </c>
       <c r="I8" s="15" t="str">
-        <v>Bible</v>
+        <v>Cigarettes</v>
       </c>
       <c r="J8" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K8" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L8" s="16">
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="4"/>
@@ -3138,24 +3144,22 @@
       <c r="C9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="4">
-        <v>2</v>
-      </c>
+      <c r="D9" s="4"/>
       <c r="E9" s="16">
         <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
-        <v>60000</v>
+        <v>0</v>
       </c>
       <c r="I9" s="15" t="str">
-        <v xml:space="preserve">  </v>
+        <v>Radio</v>
       </c>
       <c r="J9" s="4" t="str">
-        <v xml:space="preserve">  </v>
-      </c>
-      <c r="K9" s="4" t="str">
-        <v>TOTAL:</v>
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K9" s="4">
+        <v>1</v>
       </c>
       <c r="L9" s="16">
-        <v>172000</v>
+        <v>9000</v>
       </c>
       <c r="P9" s="15"/>
       <c r="Q9" s="4"/>
@@ -3169,17 +3173,23 @@
       <c r="C10" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="4">
-        <v>2</v>
-      </c>
+      <c r="D10" s="4"/>
       <c r="E10" s="16">
         <f>VLOOKUP(B10,Economy!B8:I24,8,FALSE())*D10</f>
-        <v>50000</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="I10" s="15" t="str">
+        <v>Bud</v>
+      </c>
+      <c r="J10" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K10" s="4">
+        <v>22</v>
+      </c>
+      <c r="L10" s="16">
+        <v>16500</v>
+      </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -3197,10 +3207,18 @@
         <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
         <v>0</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="16"/>
+      <c r="I11" s="15" t="str">
+        <v>Cassette</v>
+      </c>
+      <c r="J11" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K11" s="4">
+        <v>2</v>
+      </c>
+      <c r="L11" s="16">
+        <v>6000</v>
+      </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -3214,16 +3232,24 @@
         <v>38</v>
       </c>
       <c r="D12" s="4">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="E12" s="16">
         <f>VLOOKUP(B12,Economy!B10:I26,8,FALSE())*D12</f>
-        <v>2000</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="16"/>
+        <v>30000</v>
+      </c>
+      <c r="I12" s="15" t="str">
+        <v>Spray Can</v>
+      </c>
+      <c r="J12" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K12" s="4">
+        <v>2</v>
+      </c>
+      <c r="L12" s="16">
+        <v>18000</v>
+      </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
@@ -3236,15 +3262,25 @@
       <c r="C13" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
       <c r="E13" s="16">
         <f>VLOOKUP(B13,Economy!B11:I27,8,FALSE())*D13</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="16"/>
+        <v>9000</v>
+      </c>
+      <c r="I13" s="15" t="str">
+        <v>Call of the wild</v>
+      </c>
+      <c r="J13" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K13" s="4">
+        <v>1</v>
+      </c>
+      <c r="L13" s="16">
+        <v>7000</v>
+      </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -3257,15 +3293,25 @@
       <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4"/>
+      <c r="D14" s="4">
+        <v>22</v>
+      </c>
       <c r="E14" s="16">
         <f>VLOOKUP(B14,Economy!B12:I28,8,FALSE())*D14</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="16"/>
+        <v>16500</v>
+      </c>
+      <c r="I14" s="15" t="str">
+        <v>Bible</v>
+      </c>
+      <c r="J14" s="4" t="str">
+        <v xml:space="preserve"> - X</v>
+      </c>
+      <c r="K14" s="4">
+        <v>5</v>
+      </c>
+      <c r="L14" s="16">
+        <v>30000</v>
+      </c>
       <c r="P14" s="15"/>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -3278,15 +3324,25 @@
       <c r="C15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="4"/>
+      <c r="D15" s="4">
+        <v>2</v>
+      </c>
       <c r="E15" s="16">
         <f>VLOOKUP(B15,Economy!B13:I29,8,FALSE())*D15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="16"/>
+        <v>6000</v>
+      </c>
+      <c r="I15" s="15" t="str">
+        <v xml:space="preserve">  </v>
+      </c>
+      <c r="J15" s="4" t="str">
+        <v xml:space="preserve">  </v>
+      </c>
+      <c r="K15" s="4" t="str">
+        <v>TOTAL:</v>
+      </c>
+      <c r="L15" s="16">
+        <v>231500</v>
+      </c>
       <c r="P15" s="15"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -3320,10 +3376,12 @@
       <c r="C17" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="4">
+        <v>2</v>
+      </c>
       <c r="E17" s="16">
         <f>VLOOKUP(B17,Economy!B15:I31,8,FALSE())*D17</f>
-        <v>0</v>
+        <v>18000</v>
       </c>
       <c r="I17" s="15"/>
       <c r="J17" s="4"/>
@@ -3341,10 +3399,12 @@
       <c r="C18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4"/>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
       <c r="E18" s="16">
         <f>VLOOKUP(B18,Economy!B16:I32,8,FALSE())*D18</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="4"/>
@@ -3363,11 +3423,11 @@
         <v>38</v>
       </c>
       <c r="D19" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E19" s="16">
         <f>VLOOKUP(B19,Economy!B17:I33,8,FALSE())*D19</f>
-        <v>60000</v>
+        <v>30000</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="4"/>
@@ -3390,7 +3450,7 @@
       </c>
       <c r="E20" s="18">
         <f>SUM(E5:E19)</f>
-        <v>172000</v>
+        <v>231500</v>
       </c>
       <c r="I20" s="17"/>
       <c r="J20" s="15"/>
@@ -3405,7 +3465,7 @@
     <row r="22" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B22" s="20">
         <f ca="1">TODAY()</f>
-        <v>46048</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="25" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3425,27 +3485,27 @@
     <row r="26" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="J26" s="19">
         <f>$E$20/3</f>
-        <v>57333.333333333336</v>
+        <v>77166.666666666672</v>
       </c>
       <c r="K26" s="19">
         <f>$E$20/2</f>
-        <v>86000</v>
+        <v>115750</v>
       </c>
       <c r="L26" s="19">
         <f>$E$20/3</f>
-        <v>57333.333333333336</v>
+        <v>77166.666666666672</v>
       </c>
       <c r="Q26" s="19">
         <f>$E$20/3</f>
-        <v>57333.333333333336</v>
+        <v>77166.666666666672</v>
       </c>
       <c r="R26" s="19">
         <f>$E$20/2</f>
-        <v>86000</v>
+        <v>115750</v>
       </c>
       <c r="S26" s="19">
         <f>$E$20/3</f>
-        <v>57333.333333333336</v>
+        <v>77166.666666666672</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +3769,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46048</v>
+        <v>46072</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
@@ -3721,7 +3781,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46048</v>
+        <v>46072</v>
       </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
@@ -3856,7 +3916,7 @@
         <v>46</v>
       </c>
       <c r="D8" s="30">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="I8" s="9"/>
       <c r="M8" s="31">
@@ -3874,7 +3934,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="30">
-        <v>25000</v>
+        <v>37500</v>
       </c>
       <c r="I9" s="9"/>
       <c r="M9" s="30">

--- a/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
+++ b/dayzOffline.enoch/custom/28Dayz_Trader.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\twaldron\Github\7dayz\dayzOffline.enoch\custom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0BC241-F69F-4598-AC16-03EEA151E3EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FE3FD35-F690-4D4C-9E61-DF16980E1F87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales Record" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Economy" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reciept!$B$4:$E$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Reciept!$B$4:$E$24</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="149">
   <si>
     <t>Weekly Sales:</t>
   </si>
@@ -503,6 +503,18 @@
   </si>
   <si>
     <t>Rituals Books</t>
+  </si>
+  <si>
+    <t>RPG Warhead</t>
+  </si>
+  <si>
+    <t>Brake Fluid</t>
+  </si>
+  <si>
+    <t>Motor Oil</t>
+  </si>
+  <si>
+    <t>Butane Gas</t>
   </si>
 </sst>
 </file>
@@ -904,13 +916,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>304560</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>136635</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1052,13 +1064,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>8280</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>112680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
       <xdr:colOff>307440</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>232200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2717,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="11">
-        <f>VLOOKUP(B5,Economy!B4:I20,8,FALSE())*D5</f>
+        <f>VLOOKUP(B5,Economy!B4:I26,8,FALSE())*D5</f>
         <v>5500</v>
       </c>
     </row>
@@ -2732,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="11">
-        <f>VLOOKUP(B6,Economy!B5:I21,8,FALSE())*D6</f>
+        <f>VLOOKUP(B6,Economy!B5:I27,8,FALSE())*D6</f>
         <v>134400</v>
       </c>
     </row>
@@ -2747,7 +2759,7 @@
         <v>0</v>
       </c>
       <c r="E7" s="11">
-        <f>VLOOKUP(B7,Economy!B6:I22,8,FALSE())*D7</f>
+        <f>VLOOKUP(B7,Economy!B6:I28,8,FALSE())*D7</f>
         <v>0</v>
       </c>
     </row>
@@ -2762,7 +2774,7 @@
         <v>2</v>
       </c>
       <c r="E8" s="11">
-        <f>VLOOKUP(B8,Economy!B7:I23,8,FALSE())*D8</f>
+        <f>VLOOKUP(B8,Economy!B7:I29,8,FALSE())*D8</f>
         <v>60000</v>
       </c>
     </row>
@@ -2777,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="11">
-        <f>VLOOKUP(B9,Economy!B8:I24,8,FALSE())*D9</f>
+        <f>VLOOKUP(B9,Economy!B8:I30,8,FALSE())*D9</f>
         <v>0</v>
       </c>
     </row>
@@ -2792,7 +2804,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="11">
-        <f>VLOOKUP(B10,Economy!B9:I25,8,FALSE())*D10</f>
+        <f>VLOOKUP(B10,Economy!B9:I31,8,FALSE())*D10</f>
         <v>108000</v>
       </c>
     </row>
@@ -2807,7 +2819,7 @@
         <v>23</v>
       </c>
       <c r="E11" s="11">
-        <f>VLOOKUP(B11,Economy!B10:I26,8,FALSE())*D11</f>
+        <f>VLOOKUP(B11,Economy!B10:I32,8,FALSE())*D11</f>
         <v>23000</v>
       </c>
     </row>
@@ -2822,7 +2834,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="11">
-        <f>VLOOKUP(B12,Economy!B11:I27,8,FALSE())*D12</f>
+        <f>VLOOKUP(B12,Economy!B11:I33,8,FALSE())*D12</f>
         <v>18000</v>
       </c>
     </row>
@@ -2837,7 +2849,7 @@
         <v>161</v>
       </c>
       <c r="E13" s="11">
-        <f>VLOOKUP(B13,Economy!B12:I28,8,FALSE())*D13</f>
+        <f>VLOOKUP(B13,Economy!B12:I34,8,FALSE())*D13</f>
         <v>120750</v>
       </c>
     </row>
@@ -2852,7 +2864,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="11">
-        <f>VLOOKUP(B14,Economy!B13:I29,8,FALSE())*D14</f>
+        <f>VLOOKUP(B14,Economy!B13:I35,8,FALSE())*D14</f>
         <v>12000</v>
       </c>
     </row>
@@ -2867,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="11">
-        <f>VLOOKUP(B15,Economy!B14:I30,8,FALSE())*D15</f>
+        <f>VLOOKUP(B15,Economy!B14:I36,8,FALSE())*D15</f>
         <v>0</v>
       </c>
     </row>
@@ -2882,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="E16" s="11">
-        <f>VLOOKUP(B16,Economy!B15:I31,8,FALSE())*D16</f>
+        <f>VLOOKUP(B16,Economy!B15:I37,8,FALSE())*D16</f>
         <v>9000</v>
       </c>
     </row>
@@ -2897,7 +2909,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="11">
-        <f>VLOOKUP(B17,Economy!B16:I32,8,FALSE())*D17</f>
+        <f>VLOOKUP(B17,Economy!B16:I38,8,FALSE())*D17</f>
         <v>7000</v>
       </c>
     </row>
@@ -2912,7 +2924,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="11">
-        <f>VLOOKUP(B18,Economy!B17:I33,8,FALSE())*D18</f>
+        <f>VLOOKUP(B18,Economy!B17:I39,8,FALSE())*D18</f>
         <v>24000</v>
       </c>
     </row>
@@ -2930,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T30"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="22.88671875" customWidth="1"/>
@@ -2987,11 +2999,11 @@
       <c r="F3" s="13"/>
       <c r="L3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46072</v>
+        <v>46091</v>
       </c>
       <c r="S3" s="20">
         <f ca="1">TODAY()</f>
-        <v>46072</v>
+        <v>46091</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3014,24 +3026,24 @@
         <v>38</v>
       </c>
       <c r="D5" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E5" s="16">
         <f>VLOOKUP(B5,Economy!B3:I19,8,FALSE())*D5</f>
-        <v>19800</v>
+        <v>6600</v>
       </c>
       <c r="I5" s="15" t="str" cm="1">
-        <f t="array" ref="I5:L15">_xlfn._xlws.FILTER(B5:E20,E5:E20&gt;0,"")</f>
+        <f t="array" ref="I5:L14">_xlfn._xlws.FILTER(B5:E24,E5:E24&gt;0,"")</f>
         <v>Pristine Hare Pelt</v>
       </c>
       <c r="J5" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K5" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="16">
-        <v>19800</v>
+        <v>6600</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>144</v>
@@ -3055,20 +3067,20 @@
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="16">
-        <f>VLOOKUP(B6,Economy!B4:I20,8,FALSE())*D6</f>
+        <f>VLOOKUP(B6,Economy!B4:I26,8,FALSE())*D6</f>
         <v>0</v>
       </c>
       <c r="I6" s="15" t="str">
-        <v>Pristine Deer Pelt</v>
+        <v>Leather Full Stack</v>
       </c>
       <c r="J6" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K6" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L6" s="16">
-        <v>67200</v>
+        <v>12000</v>
       </c>
       <c r="P6" s="15"/>
       <c r="Q6" s="4"/>
@@ -3082,24 +3094,22 @@
       <c r="C7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="4">
-        <v>4</v>
-      </c>
+      <c r="D7" s="4"/>
       <c r="E7" s="16">
-        <f>VLOOKUP(B7,Economy!B5:I21,8,FALSE())*D7</f>
-        <v>67200</v>
+        <f>VLOOKUP(B7,Economy!B5:I27,8,FALSE())*D7</f>
+        <v>0</v>
       </c>
       <c r="I7" s="15" t="str">
-        <v>Deer Pelt</v>
+        <v>Cigarettes</v>
       </c>
       <c r="J7" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K7" s="4">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="L7" s="16">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="P7" s="15"/>
       <c r="Q7" s="4"/>
@@ -3113,24 +3123,22 @@
       <c r="C8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="4">
-        <v>2</v>
-      </c>
+      <c r="D8" s="4"/>
       <c r="E8" s="16">
-        <f>VLOOKUP(B8,Economy!B6:I22,8,FALSE())*D8</f>
-        <v>28000</v>
+        <f>VLOOKUP(B8,Economy!B6:I28,8,FALSE())*D8</f>
+        <v>0</v>
       </c>
       <c r="I8" s="15" t="str">
-        <v>Cigarettes</v>
+        <v>Radio</v>
       </c>
       <c r="J8" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K8" s="4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L8" s="16">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="P8" s="15"/>
       <c r="Q8" s="4"/>
@@ -3146,20 +3154,20 @@
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="16">
-        <f>VLOOKUP(B9,Economy!B7:I23,8,FALSE())*D9</f>
+        <f>VLOOKUP(B9,Economy!B7:I29,8,FALSE())*D9</f>
         <v>0</v>
       </c>
       <c r="I9" s="15" t="str">
-        <v>Radio</v>
+        <v>Cassette</v>
       </c>
       <c r="J9" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K9" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L9" s="16">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="P9" s="15"/>
       <c r="Q9" s="4"/>
@@ -3175,20 +3183,20 @@
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="16">
-        <f>VLOOKUP(B10,Economy!B8:I24,8,FALSE())*D10</f>
+        <f>VLOOKUP(B10,Economy!B8:I30,8,FALSE())*D10</f>
         <v>0</v>
       </c>
       <c r="I10" s="15" t="str">
-        <v>Bud</v>
+        <v>Mess  Tin</v>
       </c>
       <c r="J10" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K10" s="4">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="L10" s="16">
-        <v>16500</v>
+        <v>48000</v>
       </c>
       <c r="P10" s="15"/>
       <c r="Q10" s="4"/>
@@ -3202,13 +3210,15 @@
       <c r="C11" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4"/>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
       <c r="E11" s="16">
-        <f>VLOOKUP(B11,Economy!B9:I25,8,FALSE())*D11</f>
-        <v>0</v>
+        <f>VLOOKUP(B11,Economy!B9:I31,8,FALSE())*D11</f>
+        <v>12000</v>
       </c>
       <c r="I11" s="15" t="str">
-        <v>Cassette</v>
+        <v>Spray Can</v>
       </c>
       <c r="J11" s="4" t="str">
         <v xml:space="preserve"> - X</v>
@@ -3217,7 +3227,7 @@
         <v>2</v>
       </c>
       <c r="L11" s="16">
-        <v>6000</v>
+        <v>18000</v>
       </c>
       <c r="P11" s="15"/>
       <c r="Q11" s="4"/>
@@ -3232,23 +3242,23 @@
         <v>38</v>
       </c>
       <c r="D12" s="4">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="E12" s="16">
-        <f>VLOOKUP(B12,Economy!B10:I26,8,FALSE())*D12</f>
-        <v>30000</v>
+        <f>VLOOKUP(B12,Economy!B10:I32,8,FALSE())*D12</f>
+        <v>17000</v>
       </c>
       <c r="I12" s="15" t="str">
-        <v>Spray Can</v>
+        <v>Bible</v>
       </c>
       <c r="J12" s="4" t="str">
         <v xml:space="preserve"> - X</v>
       </c>
       <c r="K12" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L12" s="16">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="4"/>
@@ -3266,11 +3276,11 @@
         <v>1</v>
       </c>
       <c r="E13" s="16">
-        <f>VLOOKUP(B13,Economy!B11:I27,8,FALSE())*D13</f>
+        <f>VLOOKUP(B13,Economy!B11:I33,8,FALSE())*D13</f>
         <v>9000</v>
       </c>
       <c r="I13" s="15" t="str">
-        <v>Call of the wild</v>
+        <v>RPG Warhead</v>
       </c>
       <c r="J13" s="4" t="str">
         <v xml:space="preserve"> - X</v>
@@ -3279,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="L13" s="16">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="P13" s="15"/>
       <c r="Q13" s="4"/>
@@ -3293,24 +3303,22 @@
       <c r="C14" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="4">
-        <v>22</v>
-      </c>
+      <c r="D14" s="4"/>
       <c r="E14" s="16">
-        <f>VLOOKUP(B14,Economy!B12:I28,8,FALSE())*D14</f>
-        <v>16500</v>
+        <f>VLOOKUP(B14,Economy!B12:I34,8,FALSE())*D14</f>
+        <v>0</v>
       </c>
       <c r="I14" s="15" t="str">
-        <v>Bible</v>
+        <v xml:space="preserve">  </v>
       </c>
       <c r="J14" s="4" t="str">
-        <v xml:space="preserve"> - X</v>
-      </c>
-      <c r="K14" s="4">
-        <v>5</v>
+        <v xml:space="preserve">  </v>
+      </c>
+      <c r="K14" s="4" t="str">
+        <v>TOTAL:</v>
       </c>
       <c r="L14" s="16">
-        <v>30000</v>
+        <v>122600</v>
       </c>
       <c r="P14" s="15"/>
       <c r="Q14" s="4"/>
@@ -3328,21 +3336,13 @@
         <v>2</v>
       </c>
       <c r="E15" s="16">
-        <f>VLOOKUP(B15,Economy!B13:I29,8,FALSE())*D15</f>
+        <f>VLOOKUP(B15,Economy!B13:I35,8,FALSE())*D15</f>
         <v>6000</v>
       </c>
-      <c r="I15" s="15" t="str">
-        <v xml:space="preserve">  </v>
-      </c>
-      <c r="J15" s="4" t="str">
-        <v xml:space="preserve">  </v>
-      </c>
-      <c r="K15" s="4" t="str">
-        <v>TOTAL:</v>
-      </c>
-      <c r="L15" s="16">
-        <v>231500</v>
-      </c>
+      <c r="I15" s="15"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="16"/>
       <c r="P15" s="15"/>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -3355,10 +3355,12 @@
       <c r="C16" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="4"/>
+      <c r="D16" s="4">
+        <v>2</v>
+      </c>
       <c r="E16" s="16">
-        <f>VLOOKUP(B16,Economy!B14:I30,8,FALSE())*D16</f>
-        <v>0</v>
+        <f>VLOOKUP(B16,Economy!B14:I36,8,FALSE())*D16</f>
+        <v>48000</v>
       </c>
       <c r="I16" s="15"/>
       <c r="J16" s="4"/>
@@ -3380,7 +3382,7 @@
         <v>2</v>
       </c>
       <c r="E17" s="16">
-        <f>VLOOKUP(B17,Economy!B15:I31,8,FALSE())*D17</f>
+        <f>VLOOKUP(B17,Economy!B15:I37,8,FALSE())*D17</f>
         <v>18000</v>
       </c>
       <c r="I17" s="15"/>
@@ -3399,12 +3401,10 @@
       <c r="C18" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
+      <c r="D18" s="4"/>
       <c r="E18" s="16">
-        <f>VLOOKUP(B18,Economy!B16:I32,8,FALSE())*D18</f>
-        <v>7000</v>
+        <f>VLOOKUP(B18,Economy!B16:I38,8,FALSE())*D18</f>
+        <v>0</v>
       </c>
       <c r="I18" s="15"/>
       <c r="J18" s="4"/>
@@ -3423,11 +3423,11 @@
         <v>38</v>
       </c>
       <c r="D19" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="16">
-        <f>VLOOKUP(B19,Economy!B17:I33,8,FALSE())*D19</f>
-        <v>30000</v>
+        <f>VLOOKUP(B19,Economy!B17:I39,8,FALSE())*D19</f>
+        <v>6000</v>
       </c>
       <c r="I19" s="15"/>
       <c r="J19" s="4"/>
@@ -3439,77 +3439,163 @@
       <c r="S19" s="16"/>
     </row>
     <row r="20" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="16">
+        <f>VLOOKUP(B20,Economy!B18:I40,8,FALSE())*D20</f>
+        <v>9000</v>
+      </c>
+      <c r="I20" s="15"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="16"/>
+      <c r="P20" s="15"/>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="16"/>
+    </row>
+    <row r="21" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="16">
+        <f>VLOOKUP(B21,Economy!B19:I41,8,FALSE())*D21</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="15"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="16"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="4"/>
+      <c r="R21" s="4"/>
+      <c r="S21" s="16"/>
+    </row>
+    <row r="22" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B22" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="16">
+        <f>VLOOKUP(B22,Economy!B20:I42,8,FALSE())*D22</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="15"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="16"/>
+      <c r="P22" s="15"/>
+      <c r="Q22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="16"/>
+    </row>
+    <row r="23" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B23" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="16">
+        <f>VLOOKUP(B23,Economy!B21:I43,8,FALSE())*D23</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="15"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="16"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="16"/>
+    </row>
+    <row r="24" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B24" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C24" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E24" s="18">
         <f>SUM(E5:E19)</f>
-        <v>231500</v>
-      </c>
-      <c r="I20" s="17"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="18"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="18"/>
-    </row>
-    <row r="21" spans="2:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="22" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B22" s="20">
+        <v>122600</v>
+      </c>
+      <c r="I24" s="17"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="18"/>
+      <c r="P24" s="17"/>
+      <c r="Q24" s="15"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="18"/>
+    </row>
+    <row r="25" spans="2:19" ht="12.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="2:19" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="20">
         <f ca="1">TODAY()</f>
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="25" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J25" t="s">
+        <v>46091</v>
+      </c>
+    </row>
+    <row r="29" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J29" t="s">
         <v>39</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K29" t="s">
         <v>40</v>
       </c>
-      <c r="Q25" t="s">
+      <c r="Q29" t="s">
         <v>39</v>
       </c>
-      <c r="R25" t="s">
+      <c r="R29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="J26" s="19">
-        <f>$E$20/3</f>
-        <v>77166.666666666672</v>
-      </c>
-      <c r="K26" s="19">
-        <f>$E$20/2</f>
-        <v>115750</v>
-      </c>
-      <c r="L26" s="19">
-        <f>$E$20/3</f>
-        <v>77166.666666666672</v>
-      </c>
-      <c r="Q26" s="19">
-        <f>$E$20/3</f>
-        <v>77166.666666666672</v>
-      </c>
-      <c r="R26" s="19">
-        <f>$E$20/2</f>
-        <v>115750</v>
-      </c>
-      <c r="S26" s="19">
-        <f>$E$20/3</f>
-        <v>77166.666666666672</v>
+    <row r="30" spans="2:19" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="J30" s="19">
+        <f>$E$24/3</f>
+        <v>40866.666666666664</v>
+      </c>
+      <c r="K30" s="19">
+        <f>$E$24/2</f>
+        <v>61300</v>
+      </c>
+      <c r="L30" s="19">
+        <f>$E$24/3</f>
+        <v>40866.666666666664</v>
+      </c>
+      <c r="Q30" s="19">
+        <f>$E$24/3</f>
+        <v>40866.666666666664</v>
+      </c>
+      <c r="R30" s="19">
+        <f>$E$24/2</f>
+        <v>61300</v>
+      </c>
+      <c r="S30" s="19">
+        <f>$E$24/3</f>
+        <v>40866.666666666664</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B4:E20" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
+  <autoFilter ref="B4:E24" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="H2:M2"/>
@@ -3769,7 +3855,7 @@
       <c r="D15" s="23"/>
       <c r="E15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46072</v>
+        <v>46091</v>
       </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
@@ -3781,7 +3867,7 @@
       <c r="L15" s="23"/>
       <c r="M15" s="25">
         <f ca="1">TODAY()</f>
-        <v>46072</v>
+        <v>46091</v>
       </c>
       <c r="N15" s="23"/>
       <c r="O15" s="23"/>
@@ -3795,7 +3881,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -4115,6 +4201,7 @@
         <v>6000</v>
       </c>
     </row>
+    <row r="19" spans="2:14" ht="25.2" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
@@ -4444,7 +4531,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:AA52"/>
+  <dimension ref="B1:AA58"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.44140625" customWidth="1"/>
@@ -5031,237 +5118,269 @@
         <v>99</v>
       </c>
     </row>
+    <row r="19" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+      <c r="I19">
+        <v>9000</v>
+      </c>
+    </row>
     <row r="20" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" t="s">
-        <v>101</v>
-      </c>
-      <c r="M20" t="s">
-        <v>17</v>
+        <v>146</v>
+      </c>
+      <c r="I20">
+        <v>6000</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="X21" t="s">
-        <v>102</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>103</v>
-      </c>
-      <c r="Z21" t="s">
-        <v>104</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>105</v>
+      <c r="B21" t="s">
+        <v>147</v>
+      </c>
+      <c r="I21">
+        <v>36000</v>
       </c>
     </row>
     <row r="22" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
-        <v>102</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
-      </c>
-      <c r="X22" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z22" t="s">
-        <v>108</v>
-      </c>
-      <c r="AA22" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>110</v>
-      </c>
-      <c r="Z23" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B24" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y24" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="AA24" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B25" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y25" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>117</v>
+        <v>148</v>
+      </c>
+      <c r="I22">
+        <v>9000</v>
       </c>
     </row>
     <row r="26" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>115</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>119</v>
+        <v>5</v>
+      </c>
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" t="s">
+        <v>29</v>
+      </c>
+      <c r="F26" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" t="s">
+        <v>16</v>
+      </c>
+      <c r="L26" t="s">
+        <v>101</v>
+      </c>
+      <c r="M26" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="B27" t="s">
-        <v>120</v>
+      <c r="X27" t="s">
+        <v>102</v>
       </c>
       <c r="Y27" t="s">
-        <v>118</v>
+        <v>103</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
-        <v>121</v>
+        <v>102</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="X28" t="s">
+        <v>106</v>
       </c>
       <c r="Y28" t="s">
-        <v>120</v>
+        <v>107</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA28" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>103</v>
+      </c>
       <c r="Y29" t="s">
-        <v>122</v>
+        <v>110</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>111</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Y30" t="s">
-        <v>123</v>
+      <c r="B30" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y30" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA30" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="Y31" t="s">
-        <v>124</v>
+      <c r="B31" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="Y32" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="Y33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.3">
       <c r="Y34" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.3">
       <c r="Y35" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y36" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>108</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y40" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="Y41" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B37" s="6" t="s">
+    <row r="43" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B43" s="6" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B38" s="6" t="s">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B44" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B39" s="6" t="s">
+    <row r="45" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B45" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B40" s="6" t="s">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.3">
+      <c r="B46" s="6" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B42" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B43" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B44" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B46" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.3">
-      <c r="B47" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
-      <c r="B51" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
         <v>141</v>
       </c>
     </row>
